--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -20,10 +20,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Component CI Matrix'!$A$2:$V$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Framework Detail'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'InferenceMAX Workflows'!$A$2:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Runner Inventory'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Runner Inventory'!$A$7:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wheel Artifact Publishing'!$A$1:$K$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2646" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="769">
   <si>
     <t>Category</t>
   </si>
@@ -291,7 +291,7 @@
     <t>rocSHMEM</t>
   </si>
   <si>
-    <t>Test infrastructure exists in CMakeLists.txt (functional + unit tests, require MPI) but not actively triggered in TheRock CI workflows; build-only in practice</t>
+    <t>Test infra exists in CMakeLists.txt (functional + unit tests, require MPI) but no CI tests triggered in TheRock workflows; build-only in practice</t>
   </si>
   <si>
     <t>kpack</t>
@@ -414,7 +414,7 @@
     <t>ROCm SMI Lib</t>
   </si>
   <si>
-    <t>Own CI: formatting/linting only (lstt-formatting.yml); no build or test CI in TheRock pipeline; amdsmi is active successor</t>
+    <t>Own CI: formatting/linting only (lstt-formatting.yml); no build or GPU test CI in TheRock pipeline; amdsmi is active successor</t>
   </si>
   <si>
     <t>rocminfo</t>
@@ -426,7 +426,7 @@
     <t>ROCm Data Center Tool</t>
   </si>
   <si>
-    <t>dc_tools group — testing TBD</t>
+    <t>dc_tools group exists but no CI tests wired in any stage; testing TBD</t>
   </si>
   <si>
     <t>ROCm Validation Suite</t>
@@ -644,7 +644,7 @@
     <t>TheRock (iree-org/iree)</t>
   </si>
   <si>
-    <t>Direct TheRock submodule from iree-org/iree; tested indirectly via Fusilli Provider; no standalone CI test</t>
+    <t>Direct TheRock submodule from iree-org/iree; tested indirectly via Fusilli Provider; no standalone CI test or dedicated runners</t>
   </si>
   <si>
     <t>Sysdeps</t>
@@ -735,7 +735,164 @@
     <t>jaxlib from PyPI; only plugin+pjrt built from source; py 3.11–3.14; release pipeline only</t>
   </si>
   <si>
+    <t>Component CI Matrix — Unique Server Counts by Tier</t>
+  </si>
+  <si>
     <t>CI Tier</t>
+  </si>
+  <si>
+    <t>Pool Type</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Azure Build Pool (no GPU)</t>
+  </si>
+  <si>
+    <t>Physical GPU Machines</t>
+  </si>
+  <si>
+    <t>Runner Labels &amp; Counts</t>
+  </si>
+  <si>
+    <t>All Tiers</t>
+  </si>
+  <si>
+    <t>Azure Build Pool
+(cloud VMs, no GPU — compile &amp; package only)</t>
+  </si>
+  <si>
+    <t>Linux VMs: 113
+Windows VMs: 69</t>
+  </si>
+  <si>
+    <t>— (no GPU)</t>
+  </si>
+  <si>
+    <t>azure-linux-scale-rocm = 113  •  azure-windows-scale-rocm = 69</t>
+  </si>
+  <si>
+    <t>Shared across all tiers; elastic — can scale beyond snapshot count under load</t>
+  </si>
+  <si>
+    <t>Build Subtotal</t>
+  </si>
+  <si>
+    <t>182 VMs total (113 Linux + 69 Windows)</t>
+  </si>
+  <si>
+    <t>No GPU hardware</t>
+  </si>
+  <si>
+    <t>Azure-managed; no physical server count exposed</t>
+  </si>
+  <si>
+    <t>Pre-commit
+(PR)</t>
+  </si>
+  <si>
+    <t>GPU Test Pool
+(2 physical runner types)</t>
+  </si>
+  <si>
+    <t>Build VMs: 182 (shared)</t>
+  </si>
+  <si>
+    <t>95 unique nodes</t>
+  </si>
+  <si>
+    <t>linux-gfx942-1gpu-ossci-rocm (gfx94X) = 84
+windows-gfx1151-gpu-rocm (gfx1151, build-only) = 11</t>
+  </si>
+  <si>
+    <t>gfx94X: Build + Test  •  gfx1151 Win: Build-only (nightly_check_only)</t>
+  </si>
+  <si>
+    <t>Pre-commit Subtotal</t>
+  </si>
+  <si>
+    <t>182 shared build VMs</t>
+  </si>
+  <si>
+    <t>95 physical GPU</t>
+  </si>
+  <si>
+    <t>182 Azure VMs  +  95 GPU machines  =  277 total</t>
+  </si>
+  <si>
+    <t>Post-commit
+(Sub Bump)</t>
+  </si>
+  <si>
+    <t>GPU Test Pool
+(3 physical runner types)</t>
+  </si>
+  <si>
+    <t>98 unique nodes</t>
+  </si>
+  <si>
+    <t>linux-gfx942-1gpu-ossci-rocm (gfx94X) = 84
+linux-mi355-1gpu-ossci-rocm (gfx950/MI355X) = 3
+windows-gfx1151-gpu-rocm (gfx1151, build-only) = 11</t>
+  </si>
+  <si>
+    <t>Adds gfx950 (MI355X) vs Pre-commit; gfx1151 Win remains build-only</t>
+  </si>
+  <si>
+    <t>Post-commit Subtotal</t>
+  </si>
+  <si>
+    <t>98 physical GPU</t>
+  </si>
+  <si>
+    <t>182 Azure VMs  +  98 GPU machines  =  280 total</t>
+  </si>
+  <si>
+    <t>GPU Test Pool
+(13 physical runner types)</t>
+  </si>
+  <si>
+    <t>159 unique nodes</t>
+  </si>
+  <si>
+    <t>linux-gfx942-1gpu-ossci-rocm (gfx94X) = 84
+linux-gfx942-8gpu-ossci-rocm (gfx94X 8-GPU) = 4
+linux-mi355-1gpu-ossci-rocm (gfx950) = 3
+linux-gfx90a-gpu-rocm (gfx90a) = 12
+linux-gfx1030-gpu-rocm (gfx103X L) = 2
+linux-gfx110X-gpu-rocm (gfx110X L) = 6
+linux-gfx1150-gpu-rocm (gfx1150) = 1
+linux-gfx1151-gpu-rocm (gfx1151 L) = 4
+linux-gfx1153-gpu-rocm (gfx1153) = 3
+linux-gfx120X-gpu-rocm (gfx120X) = 4
+windows-gfx1151-gpu-rocm (gfx1151 W) = 11
+windows-gfx110X-gpu-rocm (gfx110X W) = 23
+windows-gfx1030-gpu-rocm (gfx103X W) = 2</t>
+  </si>
+  <si>
+    <t>Full GPU family coverage — all unique physical machines, each counted once</t>
+  </si>
+  <si>
+    <t>Nightly Subtotal</t>
+  </si>
+  <si>
+    <t>159 physical GPU</t>
+  </si>
+  <si>
+    <t>182 Azure VMs  +  159 GPU machines  =  341 total</t>
+  </si>
+  <si>
+    <t>Grand Total (all tiers, unique)</t>
+  </si>
+  <si>
+    <t>182 VMs (Azure, no GPU)</t>
+  </si>
+  <si>
+    <t>159 physical (unique GPU)</t>
+  </si>
+  <si>
+    <t>182 Azure build VMs  +  159 unique GPU machines  =  341   (each GPU machine counted once regardless of how many tiers use it)</t>
   </si>
   <si>
     <t>Trigger</t>
@@ -1131,15 +1288,48 @@
     <t>Used At</t>
   </si>
   <si>
+    <t>Physical GPU Machines by Location</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>Share %</t>
+  </si>
+  <si>
+    <t>Runner Labels</t>
+  </si>
+  <si>
+    <t>OSSCI</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>linux-gfx942-1gpu-ossci-rocm, linux-gfx942-8gpu-ossci-rocm, linux-mi355-1gpu-ossci-rocm, azure-linux-scale-rocm, azure-windows-scale-rocm</t>
+  </si>
+  <si>
+    <t>On-Prem</t>
+  </si>
+  <si>
+    <t>21%</t>
+  </si>
+  <si>
+    <t>linux-gfx90a-gpu-rocm, linux-gfx1030-gpu-rocm, linux-gfx110X-gpu-rocm, linux-gfx1150-gpu-rocm, linux-gfx1151-gpu-rocm, linux-strix-halo-gpu-rocm-oem, linux-gfx1153-gpu-rocm, linux-gfx120X-gpu-rocm, windows-gfx1151-gpu-rocm, windows-gfx110X-gpu-rocm, windows-gfx1030-gpu-rocm, nova-linux-slurm-scale-runner, rocm-asan-mi325-sandbox</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>All physical GPU runners</t>
+  </si>
+  <si>
     <t>linux-gfx942-1gpu-ossci-rocm</t>
   </si>
   <si>
-    <t>Linux</t>
-  </si>
-  <si>
-    <t>OSSCI</t>
-  </si>
-  <si>
     <t>84 (vth9c-*: 83 online + 1 offline)</t>
   </si>
   <si>
@@ -1224,9 +1414,6 @@
     <t>linux-gfx1030-gpu-rocm</t>
   </si>
   <si>
-    <t>On-Prem</t>
-  </si>
-  <si>
     <t>2 (linux-rx6950-gpu-rocm-1/2)</t>
   </si>
   <si>
@@ -1327,9 +1514,6 @@
   </si>
   <si>
     <t>windows-gfx1151-gpu-rocm</t>
-  </si>
-  <si>
-    <t>Windows</t>
   </si>
   <si>
     <t>11 (strix-halo-1/4/6/8/10-16; -7 DO-NOT-ENABLE)</t>
@@ -1648,12 +1832,42 @@
     <t>dsr1-fp8-mi355x-atom</t>
   </si>
   <si>
+    <t>dsv4-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>sgl-project/DeepSeek-V4-Pro-FP8</t>
+  </si>
+  <si>
+    <t>dsv4</t>
+  </si>
+  <si>
+    <t>sglang</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:rocm720-deepseek-v4-mi35x</t>
+  </si>
+  <si>
+    <t>dsv4-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>deepseek-ai/DeepSeek-V4-Pro</t>
+  </si>
+  <si>
+    <t>dsv4-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>mi355x-p02-g57</t>
+  </si>
+  <si>
+    <t>vllm</t>
+  </si>
+  <si>
+    <t>rocm/pytorch-private:dsv4_dsv4_adapt_upstream_0430</t>
+  </si>
+  <si>
     <t>dsr1-fp4-mi355x-sglang</t>
   </si>
   <si>
-    <t>sglang</t>
-  </si>
-  <si>
     <t>lmsysorg/sglang:v0.5.9-rocm700-mi35x</t>
   </si>
   <si>
@@ -1741,9 +1955,6 @@
     <t>int4</t>
   </si>
   <si>
-    <t>vllm</t>
-  </si>
-  <si>
     <t>aigmkt/kimi-k25-dev</t>
   </si>
   <si>
@@ -1822,7 +2033,7 @@
     <t>GPU Type</t>
   </si>
   <si>
-    <t>Node Instances</t>
+    <t>Runner Labels (all nodes)</t>
   </si>
   <si>
     <t>Node Count</t>
@@ -1834,64 +2045,22 @@
     <t>AMD</t>
   </si>
   <si>
-    <t>mi300x-amd_0, mi300x-amd_1 ...</t>
-  </si>
-  <si>
-    <t>mi300x-amd_0
-mi300x-amd_1
-mi300x-amd_2
-mi300x-amd_3
-mi300x-amd_4
-mi300x-amds_0
-mi300x-amds_1
-mi300x-amds_2
-mi300x-amds_3</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>mi300x-amd_0, mi300x-amd_1, mi300x-amd_2, mi300x-amd_3, mi300x-amd_4, mi300x-amds_0, mi300x-amds_1, mi300x-amds_2, mi300x-amds_3</t>
   </si>
   <si>
     <t>SLURM</t>
   </si>
   <si>
-    <t>mi325x-amd_0, mi325x-amd_1 ...</t>
-  </si>
-  <si>
-    <t>mi325x-amd_0
-mi325x-amd_1
-mi325x-amd_2
-mi325x-amd_3</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>mi325x-amd_0, mi325x-amd_1, mi325x-amd_2, mi325x-amd_3</t>
   </si>
   <si>
     <t>Docker/Self-hosted</t>
   </si>
   <si>
-    <t>mi355x-amd_p02g32, mi355x-amd_p02g42 ...</t>
-  </si>
-  <si>
-    <t>mi355x-amd_p02g32
-mi355x-amd_p02g42
-mi355x-amd_p02g57
-mi355x-amd_p02g44
-mi355x-amd_p01g06
-mi355x-amd_p01g07</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>mi355x-amds_0, mi355x-amds_1 ...</t>
-  </si>
-  <si>
-    <t>mi355x-amds_0
-mi355x-amds_1
-mi355x-amds_2</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2, mi355x-amds_3, mi355x-amds_4, mi355x-amds_5, mi355x-amds_6, mi355x-amds_7, mi355x-amds_8, mi355x-amd_p01_g06</t>
+  </si>
+  <si>
+    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2</t>
   </si>
   <si>
     <t>mi355x-m15-17</t>
@@ -1919,6 +2088,15 @@
   </si>
   <si>
     <t>mi355x-amds</t>
+  </si>
+  <si>
+    <t>Total AMD Inference Nodes</t>
+  </si>
+  <si>
+    <t>mi300x: 9  •  mi325x: 4  •  mi355x: 10  •  mi355x-disagg: 3  •  mi355x-m15-17: 1  •  mi355x-p02-g09: 1  •  mi355x-p02-g17: 1  •  mi355x-p02-g42: 1  •  mi355x-tw-sctrl: 1</t>
+  </si>
+  <si>
+    <t>9 GPU pool types</t>
   </si>
   <si>
     <t>InferenceMAX CI Workflows — ROCm/InferenceMAX_rocm (.github/workflows/)</t>
@@ -2316,7 +2494,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2354,11 +2532,111 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000999"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1565C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1565C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFE65100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFE65100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -2379,7 +2657,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2538,6 +2816,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD0E8F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E6C9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0B2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3F2FD"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2660,7 +2962,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2737,67 +3039,190 @@
     <xf numFmtId="0" fontId="3" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="44" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3094,13 +3519,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
     <col min="3" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="60.7109375" customWidth="1"/>
     <col min="7" max="7" width="52.7109375" customWidth="1"/>
     <col min="8" max="8" width="22.7109375" customWidth="1"/>
@@ -4578,8 +5003,8 @@
       <c r="D23" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>58</v>
+      <c r="E23" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>22</v>
@@ -5870,8 +6295,8 @@
       <c r="D42" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E42" s="11" t="s">
-        <v>58</v>
+      <c r="E42" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>22</v>
@@ -6006,8 +6431,8 @@
       <c r="D44" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>58</v>
+      <c r="E44" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>22</v>
@@ -7434,8 +7859,8 @@
       <c r="D65" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="E65" s="11" t="s">
-        <v>58</v>
+      <c r="E65" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="F65" s="23" t="s">
         <v>22</v>
@@ -8169,9 +8594,245 @@
         <v>219</v>
       </c>
     </row>
+    <row r="78" spans="1:22">
+      <c r="A78" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+      <c r="Q78" s="26"/>
+      <c r="R78" s="26"/>
+      <c r="S78" s="26"/>
+      <c r="T78" s="26"/>
+      <c r="U78" s="26"/>
+      <c r="V78" s="26"/>
+    </row>
+    <row r="79" spans="1:22">
+      <c r="A79" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="30" customHeight="1">
+      <c r="A80" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="B80" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="C80" s="29">
+        <v>182</v>
+      </c>
+      <c r="D80" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="E80" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F80" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="22" customHeight="1">
+      <c r="A81" s="27"/>
+      <c r="B81" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C81" s="33">
+        <v>182</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="E81" s="30" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" s="28"/>
+      <c r="G81" s="31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="30" customHeight="1">
+      <c r="A82" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="B82" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="C82" s="36">
+        <v>95</v>
+      </c>
+      <c r="D82" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="E82" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="F82" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="G82" s="37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="22" customHeight="1">
+      <c r="A83" s="34"/>
+      <c r="B83" s="38" t="s">
+        <v>243</v>
+      </c>
+      <c r="C83" s="39">
+        <v>95</v>
+      </c>
+      <c r="D83" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="E83" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="F83" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="G83" s="41"/>
+    </row>
+    <row r="84" spans="1:7" ht="40" customHeight="1">
+      <c r="A84" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" s="44">
+        <v>98</v>
+      </c>
+      <c r="D84" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="E84" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="F84" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="G84" s="45" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="22" customHeight="1">
+      <c r="A85" s="42"/>
+      <c r="B85" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85" s="47">
+        <v>98</v>
+      </c>
+      <c r="D85" s="48" t="s">
+        <v>244</v>
+      </c>
+      <c r="E85" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="F85" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="G85" s="49"/>
+    </row>
+    <row r="86" spans="1:7" ht="30" customHeight="1">
+      <c r="A86" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" s="52">
+        <v>159</v>
+      </c>
+      <c r="D86" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="E86" s="51" t="s">
+        <v>256</v>
+      </c>
+      <c r="F86" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="G86" s="53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="22" customHeight="1">
+      <c r="A87" s="50"/>
+      <c r="B87" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="C87" s="55">
+        <v>159</v>
+      </c>
+      <c r="D87" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="E87" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="F87" s="57" t="s">
+        <v>261</v>
+      </c>
+      <c r="G87" s="57"/>
+    </row>
+    <row r="88" spans="1:7" ht="28" customHeight="1">
+      <c r="A88" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26">
+        <v>341</v>
+      </c>
+      <c r="D88" s="58" t="s">
+        <v>263</v>
+      </c>
+      <c r="E88" s="58" t="s">
+        <v>264</v>
+      </c>
+      <c r="F88" s="58" t="s">
+        <v>265</v>
+      </c>
+      <c r="G88" s="58"/>
+    </row>
   </sheetData>
   <autoFilter ref="A2:V75"/>
-  <mergeCells count="10">
+  <mergeCells count="16">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -8182,6 +8843,12 @@
     <mergeCell ref="P1:T1"/>
     <mergeCell ref="U1:U2"/>
     <mergeCell ref="V1:V2"/>
+    <mergeCell ref="A78:V78"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:B88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8204,144 +8871,144 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>223</v>
+        <v>268</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>224</v>
+        <v>269</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>227</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="70" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>235</v>
+      <c r="B2" s="59" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>275</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>277</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>278</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="42" customHeight="1">
       <c r="A3" s="25" t="s">
-        <v>236</v>
+        <v>281</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>240</v>
+        <v>285</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="42" customHeight="1">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>244</v>
+      <c r="B4" s="60" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>291</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>294</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>295</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>288</v>
+      </c>
+      <c r="I4" s="60" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28" customHeight="1">
       <c r="A5" s="16" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>22</v>
@@ -8349,31 +9016,31 @@
     </row>
     <row r="6" spans="1:9" ht="42" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -8402,410 +9069,410 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="140" customHeight="1">
-      <c r="A2" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="L2" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="M2" s="26" t="s">
-        <v>288</v>
+      <c r="A2" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="K2" s="59" t="s">
+        <v>331</v>
+      </c>
+      <c r="L2" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="M2" s="59" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="196" customHeight="1">
-      <c r="A3" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="L3" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>298</v>
+      <c r="A3" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="G3" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="H3" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="I3" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="J3" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="K3" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="L3" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="M3" s="59" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="196" customHeight="1">
-      <c r="A4" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>301</v>
+      <c r="A4" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>345</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="I4" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="J4" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="K4" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="L4" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="M4" s="59" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="196" customHeight="1">
-      <c r="A5" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="M5" s="26"/>
+      <c r="A5" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="H5" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="I5" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="J5" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="K5" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="L5" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="M5" s="59"/>
     </row>
     <row r="6" spans="1:13" ht="196" customHeight="1">
-      <c r="A6" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>295</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>306</v>
+      <c r="A6" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="I6" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="J6" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="K6" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="L6" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="M6" s="59" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="42" customHeight="1">
       <c r="A7" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>312</v>
+        <v>357</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="K7" s="25" t="s">
         <v>168</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="42" customHeight="1">
       <c r="A8" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="K8" s="25" t="s">
         <v>168</v>
       </c>
       <c r="L8" s="25" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>320</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="42" customHeight="1">
       <c r="A9" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>322</v>
+        <v>367</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="K9" s="25" t="s">
         <v>168</v>
       </c>
       <c r="L9" s="25" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>320</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="42" customHeight="1">
       <c r="A10" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>323</v>
+        <v>368</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="K10" s="25" t="s">
         <v>168</v>
       </c>
       <c r="L10" s="25" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -8816,15 +9483,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="34.7109375" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="6" max="6" width="80.7109375" customWidth="1"/>
     <col min="7" max="7" width="29.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" customWidth="1"/>
@@ -8832,846 +9499,941 @@
     <col min="11" max="11" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:11" ht="26" customHeight="1">
+      <c r="A1" s="26" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+    </row>
+    <row r="2" spans="1:11" ht="22" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="20" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="61">
+        <v>273</v>
+      </c>
+      <c r="C3" s="61">
+        <v>204</v>
+      </c>
+      <c r="D3" s="61">
+        <v>69</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="20" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="63">
+        <v>74</v>
+      </c>
+      <c r="C4" s="63">
+        <v>38</v>
+      </c>
+      <c r="D4" s="63">
+        <v>36</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>390</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="22" customHeight="1">
+      <c r="B5" s="1">
+        <v>347</v>
+      </c>
+      <c r="C5" s="1">
+        <v>242</v>
+      </c>
+      <c r="D5" s="1">
+        <v>105</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="22" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="20" customHeight="1">
-      <c r="A2" s="15">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="K2" s="15" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="20" customHeight="1">
-      <c r="A3" s="15">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="J3" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="20" customHeight="1">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>341</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="20" customHeight="1">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="20" customHeight="1">
-      <c r="A6" s="15">
-        <v>5</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>359</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="20" customHeight="1">
-      <c r="A7" s="15">
-        <v>6</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="20" customHeight="1">
       <c r="A8" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="20" customHeight="1">
       <c r="A9" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20" customHeight="1">
       <c r="A10" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>337</v>
-      </c>
       <c r="D10" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="20" customHeight="1">
       <c r="A11" s="15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="20" customHeight="1">
       <c r="A12" s="15">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>364</v>
+        <v>420</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="20" customHeight="1">
       <c r="A13" s="15">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="G13" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="I13" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="H13" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>342</v>
-      </c>
       <c r="J13" s="15" t="s">
-        <v>364</v>
+        <v>420</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="20" customHeight="1">
-      <c r="A14" s="18">
-        <v>13</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>403</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>404</v>
+      <c r="A14" s="15">
+        <v>7</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20" customHeight="1">
-      <c r="A15" s="18">
-        <v>14</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>406</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>375</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>407</v>
+      <c r="A15" s="15">
+        <v>8</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="20" customHeight="1">
-      <c r="A16" s="18">
-        <v>15</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="K16" s="18"/>
+      <c r="A16" s="15">
+        <v>9</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="20" customHeight="1">
-      <c r="A17" s="18">
-        <v>16</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>411</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>412</v>
-      </c>
-      <c r="G17" s="18" t="s">
+      <c r="A17" s="15">
+        <v>10</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="I17" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="H17" s="18" t="s">
-        <v>399</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>413</v>
+      <c r="J17" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="20" customHeight="1">
       <c r="A18" s="15">
+        <v>11</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="20" customHeight="1">
+      <c r="A19" s="15">
+        <v>12</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="20" customHeight="1">
+      <c r="A20" s="18">
+        <v>13</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="H20" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="20" customHeight="1">
+      <c r="A21" s="18">
+        <v>14</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="20" customHeight="1">
+      <c r="A22" s="18">
+        <v>15</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="23" spans="1:11" ht="20" customHeight="1">
+      <c r="A23" s="18">
+        <v>16</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="20" customHeight="1">
+      <c r="A24" s="15">
         <v>17</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B24" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="20" customHeight="1">
-      <c r="A19" s="18">
+      <c r="C24" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="20" customHeight="1">
+      <c r="A25" s="18">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B25" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="K19" s="18" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="20" customHeight="1">
-      <c r="A20" s="15">
+      <c r="C25" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="20" customHeight="1">
+      <c r="A26" s="15">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="20" customHeight="1">
-      <c r="A21" s="15">
+      <c r="B26" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>477</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="20" customHeight="1">
+      <c r="A27" s="15">
         <v>20</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>342</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="20" customHeight="1">
-      <c r="A22" s="15">
+      <c r="B27" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="20" customHeight="1">
+      <c r="A28" s="15">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="20" customHeight="1">
-      <c r="A23" s="15">
-        <v>22</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="20" customHeight="1">
-      <c r="A24" s="18">
+      <c r="B28" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="20" customHeight="1">
+      <c r="A29" s="15">
+        <v>22</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="20" customHeight="1">
+      <c r="A30" s="18">
         <v>23</v>
       </c>
-      <c r="B24" s="18" t="s">
-        <v>445</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>402</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>441</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>442</v>
-      </c>
-      <c r="H24" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>446</v>
-      </c>
-      <c r="K24" s="18" t="s">
-        <v>444</v>
+      <c r="B30" s="18" t="s">
+        <v>499</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>495</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>500</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K24"/>
+  <autoFilter ref="A7:K30"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9696,234 +10458,234 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>226</v>
+        <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>447</v>
+        <v>501</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>448</v>
+        <v>502</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>450</v>
+        <v>504</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="28" customHeight="1">
-      <c r="A2" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>452</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>453</v>
-      </c>
-      <c r="F2" s="26" t="s">
-        <v>454</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>456</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="K2" s="26" t="s">
-        <v>458</v>
+      <c r="A2" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>506</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>507</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>508</v>
+      </c>
+      <c r="G2" s="59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>510</v>
+      </c>
+      <c r="I2" s="59" t="s">
+        <v>331</v>
+      </c>
+      <c r="J2" s="59" t="s">
+        <v>511</v>
+      </c>
+      <c r="K2" s="59" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="28" customHeight="1">
-      <c r="A3" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="K3" s="26"/>
+      <c r="A3" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>513</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>514</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>515</v>
+      </c>
+      <c r="G3" s="59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H3" s="59" t="s">
+        <v>516</v>
+      </c>
+      <c r="I3" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="J3" s="59" t="s">
+        <v>511</v>
+      </c>
+      <c r="K3" s="59"/>
     </row>
     <row r="4" spans="1:11" ht="28" customHeight="1">
-      <c r="A4" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>299</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>463</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>464</v>
+      <c r="A4" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>513</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>514</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>515</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H4" s="59" t="s">
+        <v>517</v>
+      </c>
+      <c r="I4" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="J4" s="59" t="s">
+        <v>511</v>
+      </c>
+      <c r="K4" s="59" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="28" customHeight="1">
-      <c r="A5" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>465</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="K5" s="26"/>
+      <c r="A5" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>347</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>513</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>514</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>515</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H5" s="59" t="s">
+        <v>519</v>
+      </c>
+      <c r="I5" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="J5" s="59" t="s">
+        <v>511</v>
+      </c>
+      <c r="K5" s="59"/>
     </row>
     <row r="6" spans="1:11" ht="28" customHeight="1">
-      <c r="A6" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>460</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>455</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>457</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>306</v>
+      <c r="A6" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>513</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>514</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>515</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>509</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>520</v>
+      </c>
+      <c r="I6" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="J6" s="59" t="s">
+        <v>511</v>
+      </c>
+      <c r="K6" s="59" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20" customHeight="1">
       <c r="A7" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>452</v>
+        <v>506</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>467</v>
+        <v>521</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>168</v>
@@ -9932,33 +10694,33 @@
         <v>22</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="20" customHeight="1">
       <c r="A8" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>452</v>
+        <v>506</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>467</v>
+        <v>521</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>168</v>
@@ -9967,33 +10729,33 @@
         <v>22</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="20" customHeight="1">
       <c r="A9" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>452</v>
+        <v>506</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>467</v>
+        <v>521</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>168</v>
@@ -10002,33 +10764,33 @@
         <v>22</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20" customHeight="1">
       <c r="A10" s="25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>323</v>
+        <v>368</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>452</v>
+        <v>506</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>470</v>
+        <v>524</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>455</v>
+        <v>509</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>168</v>
@@ -10037,7 +10799,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -10048,7 +10810,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -10062,598 +10824,598 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>471</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="A1" s="65" t="s">
+        <v>525</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="28" t="s">
-        <v>472</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>473</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>475</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>476</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="H2" s="28" t="s">
-        <v>478</v>
+      <c r="A2" s="65" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>527</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>528</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>529</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>530</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>311</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>531</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" customHeight="1">
       <c r="A3" s="20" t="s">
-        <v>479</v>
+        <v>533</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>480</v>
+        <v>534</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>481</v>
+        <v>535</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G3" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G3" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>485</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>488</v>
+        <v>542</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>489</v>
+        <v>543</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G4" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G4" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>490</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>491</v>
+        <v>545</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>492</v>
+        <v>546</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>493</v>
+        <v>547</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G5" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G5" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>490</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>494</v>
+        <v>548</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>495</v>
+        <v>549</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>496</v>
+        <v>550</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>489</v>
+        <v>543</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G6" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G6" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>490</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>497</v>
+        <v>551</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>498</v>
+        <v>552</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>489</v>
+        <v>543</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G7" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G7" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>501</v>
+        <v>555</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G8" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G8" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>503</v>
+        <v>557</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>489</v>
+        <v>543</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G9" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G9" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>505</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>506</v>
+        <v>560</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>502</v>
+        <v>556</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G10" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G10" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>505</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>507</v>
+        <v>561</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>504</v>
+        <v>562</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G11" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G11" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>509</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>510</v>
+        <v>566</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>502</v>
+        <v>567</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G12" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G12" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>512</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>513</v>
+        <v>568</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>502</v>
+        <v>567</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>499</v>
+        <v>563</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G13" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G13" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>512</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>515</v>
+        <v>572</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>502</v>
+        <v>558</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G14" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G14" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>509</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>516</v>
+        <v>574</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G15" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G15" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>520</v>
+        <v>576</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>521</v>
+        <v>577</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>482</v>
+        <v>578</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G16" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G16" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>522</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>523</v>
+        <v>579</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>517</v>
+        <v>556</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>518</v>
+        <v>553</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G17" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G17" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>524</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>517</v>
+        <v>581</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>519</v>
+        <v>583</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G18" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G18" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>524</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="16" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>526</v>
+        <v>585</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>527</v>
+        <v>581</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>483</v>
+        <v>583</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G19" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="G19" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>524</v>
+        <v>586</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="16" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>527</v>
+        <v>581</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>483</v>
+        <v>583</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G20" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G20" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>529</v>
+        <v>588</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="16" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>530</v>
+        <v>589</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>527</v>
+        <v>581</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>482</v>
+        <v>578</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>483</v>
+        <v>583</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="G21" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G21" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>522</v>
+        <v>588</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>527</v>
+        <v>591</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>518</v>
+        <v>582</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>511</v>
+        <v>578</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G22" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G22" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>524</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>532</v>
+        <v>592</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>480</v>
+        <v>591</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>481</v>
+        <v>582</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>482</v>
+        <v>536</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>483</v>
+        <v>537</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="G23" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G23" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>533</v>
+        <v>593</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="16" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>534</v>
+        <v>594</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>535</v>
+        <v>591</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>488</v>
+        <v>582</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>536</v>
@@ -10664,327 +11426,405 @@
       <c r="F24" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>539</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="16" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>540</v>
+        <v>595</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>535</v>
+        <v>591</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>488</v>
+        <v>582</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>514</v>
+        <v>575</v>
       </c>
       <c r="E25" s="20" t="s">
         <v>537</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G25" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G25" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>541</v>
+        <v>588</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>542</v>
+        <v>596</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>487</v>
+        <v>534</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>488</v>
+        <v>535</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G26" s="29" t="s">
+        <v>564</v>
+      </c>
+      <c r="G26" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>541</v>
+        <v>597</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16" customHeight="1">
       <c r="A27" s="20" t="s">
-        <v>544</v>
+        <v>598</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>492</v>
+        <v>599</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>493</v>
+        <v>542</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>482</v>
+        <v>600</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>483</v>
+        <v>601</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G27" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G27" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>545</v>
+        <v>602</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="16" customHeight="1">
       <c r="A28" s="20" t="s">
-        <v>546</v>
+        <v>603</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>492</v>
+        <v>599</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>493</v>
+        <v>542</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>511</v>
+        <v>578</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>483</v>
+        <v>601</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G28" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G28" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>547</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="16" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>548</v>
+        <v>605</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>492</v>
+        <v>541</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>493</v>
+        <v>542</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>514</v>
+        <v>606</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G29" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G29" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>547</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="16" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>495</v>
+        <v>546</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G30" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G30" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>550</v>
+        <v>608</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16" customHeight="1">
       <c r="A31" s="20" t="s">
-        <v>551</v>
+        <v>609</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>495</v>
+        <v>546</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>514</v>
+        <v>575</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G31" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G31" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>550</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>552</v>
+        <v>611</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>482</v>
+        <v>578</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G32" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="G32" s="66" t="s">
         <v>66</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>550</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" customHeight="1">
       <c r="A33" s="20" t="s">
-        <v>554</v>
+        <v>612</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>502</v>
+        <v>549</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>19</v>
+        <v>570</v>
+      </c>
+      <c r="G33" s="66" t="s">
+        <v>66</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>557</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" customHeight="1">
       <c r="A34" s="20" t="s">
-        <v>558</v>
+        <v>614</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>502</v>
+        <v>549</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>483</v>
+        <v>543</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>19</v>
+        <v>570</v>
+      </c>
+      <c r="G34" s="66" t="s">
+        <v>66</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>557</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16" customHeight="1">
       <c r="A35" s="20" t="s">
-        <v>559</v>
+        <v>615</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>560</v>
+        <v>616</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>499</v>
+        <v>550</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>489</v>
+        <v>543</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>19</v>
+        <v>570</v>
+      </c>
+      <c r="G35" s="66" t="s">
+        <v>66</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>561</v>
+        <v>613</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" customHeight="1">
       <c r="A36" s="20" t="s">
-        <v>562</v>
+        <v>617</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>555</v>
+        <v>618</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>556</v>
+        <v>619</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>19</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>561</v>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="16" customHeight="1">
+      <c r="A37" s="20" t="s">
+        <v>621</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>556</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>537</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="16" customHeight="1">
+      <c r="A38" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="16" customHeight="1">
+      <c r="A39" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H36"/>
+  <autoFilter ref="A2:H39"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -10994,219 +11834,206 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="70.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="30" t="s">
-        <v>563</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>564</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>328</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>566</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="126" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>511</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="56" customHeight="1">
-      <c r="A3" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>514</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>573</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="E3" s="20" t="s">
+    <row r="1" spans="1:5" ht="26" customHeight="1">
+      <c r="A1" s="67" t="s">
+        <v>626</v>
+      </c>
+      <c r="B1" s="67" t="s">
+        <v>627</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>628</v>
+      </c>
+      <c r="D1" s="67" t="s">
+        <v>629</v>
+      </c>
+      <c r="E1" s="67" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20" customHeight="1">
+      <c r="A2" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B2" s="68" t="s">
         <v>575</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="84" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="D4" s="20" t="s">
+      <c r="C2" s="69" t="s">
+        <v>632</v>
+      </c>
+      <c r="D2" s="70">
+        <v>9</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20" customHeight="1">
+      <c r="A3" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B3" s="68" t="s">
         <v>578</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>579</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="42" customHeight="1">
-      <c r="A5" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>584</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>584</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="20" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>586</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>586</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="20" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>587</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>588</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="20" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>589</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>589</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>590</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>572</v>
+      <c r="C3" s="69" t="s">
+        <v>634</v>
+      </c>
+      <c r="D3" s="70">
+        <v>4</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1">
+      <c r="A4" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>636</v>
+      </c>
+      <c r="D4" s="70">
+        <v>10</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20" customHeight="1">
+      <c r="A5" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>618</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>637</v>
+      </c>
+      <c r="D5" s="70">
+        <v>3</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1">
+      <c r="A6" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>638</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>639</v>
+      </c>
+      <c r="D6" s="70">
+        <v>1</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1">
+      <c r="A7" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>640</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>641</v>
+      </c>
+      <c r="D7" s="70">
+        <v>1</v>
+      </c>
+      <c r="E7" s="68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1">
+      <c r="A8" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>642</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>643</v>
+      </c>
+      <c r="D8" s="70">
+        <v>1</v>
+      </c>
+      <c r="E8" s="68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20" customHeight="1">
+      <c r="A9" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>606</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>644</v>
+      </c>
+      <c r="D9" s="70">
+        <v>1</v>
+      </c>
+      <c r="E9" s="68" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>631</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>645</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>646</v>
+      </c>
+      <c r="D10" s="70">
+        <v>1</v>
+      </c>
+      <c r="E10" s="68" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28" customHeight="1">
+      <c r="A11" s="71" t="s">
+        <v>647</v>
+      </c>
+      <c r="B11" s="71"/>
+      <c r="C11" s="72" t="s">
+        <v>648</v>
+      </c>
+      <c r="D11" s="71">
+        <v>31</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>649</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:E10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A11:B11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11222,327 +12049,327 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="28" t="s">
-        <v>592</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
+      <c r="A1" s="65" t="s">
+        <v>650</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="28" t="s">
-        <v>593</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>594</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>595</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>596</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>597</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>598</v>
-      </c>
-      <c r="G2" s="28" t="s">
-        <v>599</v>
-      </c>
-      <c r="H2" s="28" t="s">
+      <c r="A2" s="65" t="s">
+        <v>651</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>652</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>653</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>654</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>655</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>656</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>657</v>
+      </c>
+      <c r="H2" s="65" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="182" customHeight="1">
-      <c r="A3" s="31" t="s">
-        <v>600</v>
+      <c r="A3" s="73" t="s">
+        <v>658</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>602</v>
+        <v>659</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>660</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>603</v>
+        <v>661</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>605</v>
+        <v>663</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>606</v>
+        <v>664</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>607</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1">
-      <c r="A4" s="31" t="s">
-        <v>608</v>
+      <c r="A4" s="73" t="s">
+        <v>666</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>610</v>
+        <v>667</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>668</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>611</v>
+        <v>669</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>612</v>
+        <v>670</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>613</v>
+        <v>671</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>614</v>
+        <v>672</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>615</v>
+      <c r="A5" s="73" t="s">
+        <v>673</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>610</v>
+        <v>674</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>668</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>611</v>
+        <v>669</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>617</v>
+        <v>675</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>613</v>
+        <v>671</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>618</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="84" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>613</v>
+      <c r="A6" s="73" t="s">
+        <v>671</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>620</v>
+        <v>677</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>678</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>621</v>
+        <v>679</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>622</v>
+        <v>680</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>606</v>
+        <v>664</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>623</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>624</v>
+      <c r="A7" s="73" t="s">
+        <v>682</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>626</v>
+        <v>683</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>684</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>627</v>
+        <v>685</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>628</v>
+        <v>686</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>629</v>
+        <v>687</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>630</v>
+        <v>688</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>631</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>632</v>
+      <c r="A8" s="73" t="s">
+        <v>690</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>633</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>634</v>
+        <v>691</v>
+      </c>
+      <c r="C8" s="74" t="s">
+        <v>692</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>635</v>
+        <v>693</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>636</v>
+        <v>694</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>637</v>
+        <v>695</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>638</v>
+        <v>696</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>639</v>
+      <c r="A9" s="73" t="s">
+        <v>697</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>640</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>641</v>
+        <v>698</v>
+      </c>
+      <c r="C9" s="74" t="s">
+        <v>699</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>642</v>
+        <v>700</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>643</v>
+        <v>701</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>644</v>
+        <v>702</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>645</v>
+        <v>703</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1">
-      <c r="A10" s="33" t="s">
-        <v>646</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>647</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>648</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>649</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>650</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>651</v>
+      <c r="A10" s="75" t="s">
+        <v>704</v>
+      </c>
+      <c r="B10" s="76" t="s">
+        <v>705</v>
+      </c>
+      <c r="C10" s="74" t="s">
+        <v>706</v>
+      </c>
+      <c r="D10" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>707</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>708</v>
+      </c>
+      <c r="G10" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="76" t="s">
+        <v>709</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1">
-      <c r="A11" s="33" t="s">
-        <v>652</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>653</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>648</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>654</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>655</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>656</v>
+      <c r="A11" s="75" t="s">
+        <v>710</v>
+      </c>
+      <c r="B11" s="76" t="s">
+        <v>711</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>706</v>
+      </c>
+      <c r="D11" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>712</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>713</v>
+      </c>
+      <c r="G11" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="76" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1">
-      <c r="A12" s="33" t="s">
-        <v>657</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>658</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>659</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>660</v>
-      </c>
-      <c r="F12" s="34" t="s">
-        <v>661</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>662</v>
+      <c r="A12" s="75" t="s">
+        <v>715</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>716</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>717</v>
+      </c>
+      <c r="D12" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>718</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>719</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="76" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1">
-      <c r="A13" s="33" t="s">
-        <v>663</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>664</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>665</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>666</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>667</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>668</v>
+      <c r="A13" s="75" t="s">
+        <v>721</v>
+      </c>
+      <c r="B13" s="76" t="s">
+        <v>722</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>723</v>
+      </c>
+      <c r="D13" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>724</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>725</v>
+      </c>
+      <c r="G13" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="76" t="s">
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -11568,172 +12395,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>669</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
+      <c r="A1" s="26" t="s">
+        <v>727</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
-      <c r="A2" s="35" t="s">
-        <v>670</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>671</v>
-      </c>
-      <c r="C2" s="35" t="s">
-        <v>672</v>
+      <c r="A2" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>729</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="22" customHeight="1">
-      <c r="A3" s="36" t="s">
-        <v>673</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>674</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>675</v>
+      <c r="A3" s="77" t="s">
+        <v>731</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>732</v>
+      </c>
+      <c r="C3" s="79" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
-      <c r="A4" s="39" t="s">
-        <v>676</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>677</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>678</v>
+      <c r="A4" s="80" t="s">
+        <v>734</v>
+      </c>
+      <c r="B4" s="79" t="s">
+        <v>735</v>
+      </c>
+      <c r="C4" s="79" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1">
-      <c r="A5" s="39" t="s">
-        <v>679</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>680</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>681</v>
+      <c r="A5" s="80" t="s">
+        <v>737</v>
+      </c>
+      <c r="B5" s="79" t="s">
+        <v>738</v>
+      </c>
+      <c r="C5" s="79" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1">
-      <c r="A6" s="39" t="s">
-        <v>682</v>
-      </c>
-      <c r="B6" s="38" t="s">
-        <v>683</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>684</v>
+      <c r="A6" s="80" t="s">
+        <v>740</v>
+      </c>
+      <c r="B6" s="79" t="s">
+        <v>741</v>
+      </c>
+      <c r="C6" s="79" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>685</v>
-      </c>
-      <c r="B7" s="38" t="s">
-        <v>686</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>687</v>
+      <c r="A7" s="80" t="s">
+        <v>743</v>
+      </c>
+      <c r="B7" s="79" t="s">
+        <v>744</v>
+      </c>
+      <c r="C7" s="79" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1">
-      <c r="A8" s="39" t="s">
-        <v>688</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>689</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>690</v>
+      <c r="A8" s="80" t="s">
+        <v>746</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>747</v>
+      </c>
+      <c r="C8" s="79" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="22" customHeight="1">
-      <c r="A9" s="39" t="s">
-        <v>691</v>
-      </c>
-      <c r="B9" s="38" t="s">
-        <v>692</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>693</v>
+      <c r="A9" s="80" t="s">
+        <v>749</v>
+      </c>
+      <c r="B9" s="79" t="s">
+        <v>750</v>
+      </c>
+      <c r="C9" s="79" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="22" customHeight="1">
-      <c r="A10" s="39" t="s">
-        <v>694</v>
-      </c>
-      <c r="B10" s="38" t="s">
-        <v>695</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>696</v>
+      <c r="A10" s="80" t="s">
+        <v>752</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>753</v>
+      </c>
+      <c r="C10" s="79" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1">
-      <c r="A11" s="40" t="s">
-        <v>697</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>698</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>699</v>
+      <c r="A11" s="81" t="s">
+        <v>755</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>756</v>
+      </c>
+      <c r="C11" s="79" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22" customHeight="1">
-      <c r="A12" s="42" t="s">
-        <v>697</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>700</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>701</v>
+      <c r="A12" s="83" t="s">
+        <v>755</v>
+      </c>
+      <c r="B12" s="84" t="s">
+        <v>758</v>
+      </c>
+      <c r="C12" s="79" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1">
-      <c r="A13" s="44" t="s">
-        <v>702</v>
-      </c>
-      <c r="B13" s="45" t="s">
-        <v>703</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>704</v>
+      <c r="A13" s="85" t="s">
+        <v>760</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>761</v>
+      </c>
+      <c r="C13" s="79" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="22" customHeight="1">
-      <c r="A14" s="39" t="s">
-        <v>705</v>
-      </c>
-      <c r="B14" s="38" t="s">
-        <v>706</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>707</v>
+      <c r="A14" s="80" t="s">
+        <v>763</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>764</v>
+      </c>
+      <c r="C14" s="79" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1">
-      <c r="A15" s="39" t="s">
-        <v>708</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>709</v>
-      </c>
-      <c r="C15" s="46" t="s">
+      <c r="A15" s="80" t="s">
+        <v>766</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>767</v>
+      </c>
+      <c r="C15" s="87" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1">
-      <c r="A16" s="46" t="s">
-        <v>710</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
+      <c r="A16" s="87" t="s">
+        <v>768</v>
+      </c>
+      <c r="B16" s="87"/>
+      <c r="C16" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -20,9 +20,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Component CI Matrix'!$A$2:$V$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Framework Detail'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'InferenceMAX Workflows'!$A$2:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Runner Inventory'!$A$7:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wheel Artifact Publishing'!$A$1:$K$10</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2732" uniqueCount="769">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="687">
   <si>
     <t>Category</t>
   </si>
@@ -1300,33 +1300,24 @@
     <t>Share %</t>
   </si>
   <si>
-    <t>Runner Labels</t>
-  </si>
-  <si>
     <t>OSSCI</t>
   </si>
   <si>
     <t>79%</t>
   </si>
   <si>
-    <t>linux-gfx942-1gpu-ossci-rocm, linux-gfx942-8gpu-ossci-rocm, linux-mi355-1gpu-ossci-rocm, azure-linux-scale-rocm, azure-windows-scale-rocm</t>
-  </si>
-  <si>
     <t>On-Prem</t>
   </si>
   <si>
     <t>21%</t>
   </si>
   <si>
-    <t>linux-gfx90a-gpu-rocm, linux-gfx1030-gpu-rocm, linux-gfx110X-gpu-rocm, linux-gfx1150-gpu-rocm, linux-gfx1151-gpu-rocm, linux-strix-halo-gpu-rocm-oem, linux-gfx1153-gpu-rocm, linux-gfx120X-gpu-rocm, windows-gfx1151-gpu-rocm, windows-gfx110X-gpu-rocm, windows-gfx1030-gpu-rocm, nova-linux-slurm-scale-runner, rocm-asan-mi325-sandbox</t>
+    <t>Total</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>All physical GPU runners</t>
-  </si>
-  <si>
     <t>linux-gfx942-1gpu-ossci-rocm</t>
   </si>
   <si>
@@ -1646,6 +1637,99 @@
   </si>
   <si>
     <t>Fallback / fork CI</t>
+  </si>
+  <si>
+    <t>Framework Runner &amp; Server Count Details</t>
+  </si>
+  <si>
+    <t>Pool</t>
+  </si>
+  <si>
+    <t>Build (VMs)</t>
+  </si>
+  <si>
+    <t>GPU Test (Physical)</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t>Build Pool (2 VM pools, no GPU)</t>
+  </si>
+  <si>
+    <t>azure-linux-scale-rocm = 113 VMs  •  azure-windows-scale-rocm = 69 VMs</t>
+  </si>
+  <si>
+    <t>Elastic; auto-scales under load; used for all compile/package jobs</t>
+  </si>
+  <si>
+    <t>GPU Test Pool (13 physical runner types)</t>
+  </si>
+  <si>
+    <t>— (no build VMs here)</t>
+  </si>
+  <si>
+    <t>159 unique physical machines</t>
+  </si>
+  <si>
+    <t>linux-gfx942-1gpu-ossci-rocm = 84  •  linux-gfx942-8gpu-ossci-rocm = 4  •  linux-mi355-1gpu-ossci-rocm = 3  •  linux-gfx90a-gpu-rocm = 12  •  linux-gfx1030-gpu-rocm = 2  •  linux-gfx110X-gpu-rocm = 6  •  linux-gfx1150-gpu-rocm = 1  •  linux-gfx1151-gpu-rocm = 4  •  linux-gfx1153-gpu-rocm = 3  •  linux-gfx120X-gpu-rocm = 4  •  windows-gfx1151-gpu-rocm = 11  •  windows-gfx110X-gpu-rocm = 23  •  windows-gfx1030-gpu-rocm = 2</t>
+  </si>
+  <si>
+    <t>5 PyTorch versions × 5 Python vers × 13 GPU runner types</t>
+  </si>
+  <si>
+    <t>PyTorch Total</t>
+  </si>
+  <si>
+    <t>182 build VMs</t>
+  </si>
+  <si>
+    <t>182 build VMs + 159 physical GPU machines = 341</t>
+  </si>
+  <si>
+    <t>Mixed: VMs + physical</t>
+  </si>
+  <si>
+    <t>Build + Test (shared build VM pool)</t>
+  </si>
+  <si>
+    <t>Shared with PyTorch — azure-linux-scale-rocm (not counted separately)</t>
+  </si>
+  <si>
+    <t>84 physical (gfx94X only)</t>
+  </si>
+  <si>
+    <t>linux-gfx942-1gpu-ossci-rocm = 84 physical  |  Build: shared azure-linux-scale-rocm VMs</t>
+  </si>
+  <si>
+    <t>4 JAX versions × 4 Python vers × 1 GPU runner type</t>
+  </si>
+  <si>
+    <t>JAX Total</t>
+  </si>
+  <si>
+    <t>Build VMs shared with PyTorch — not counted separately</t>
+  </si>
+  <si>
+    <t>84 physical only</t>
+  </si>
+  <si>
+    <t>84 dedicated physical GPU machines + shared build VM pool (counted under PyTorch)</t>
+  </si>
+  <si>
+    <t>JAX reuses linux-gfx942-1gpu-ossci-rocm from PyTorch pool</t>
+  </si>
+  <si>
+    <t>Grand Total (PyTorch + JAX)</t>
+  </si>
+  <si>
+    <t>182 VMs (shared build pool)</t>
+  </si>
+  <si>
+    <t>159 physical (unique GPU machines; JAX shares PyTorch pool)</t>
+  </si>
+  <si>
+    <t>182 shared build VMs + 159 unique physical GPU machines = 341   |   GPU node counts per tier — each physical machine counted once</t>
   </si>
   <si>
     <t>Wheel Packages</t>
@@ -1748,285 +1832,6 @@
     <t>Pinned Docker Image</t>
   </si>
   <si>
-    <t>glm5-fp8-mi355x-atom</t>
-  </si>
-  <si>
-    <t>zai-org/GLM-5-FP8</t>
-  </si>
-  <si>
-    <t>glm5</t>
-  </si>
-  <si>
-    <t>mi355x</t>
-  </si>
-  <si>
-    <t>fp8</t>
-  </si>
-  <si>
-    <t>atom</t>
-  </si>
-  <si>
-    <t>rocm/atom-dev:nightly_202603291522</t>
-  </si>
-  <si>
-    <t>kimik2.5-fp4-mi355x-atom</t>
-  </si>
-  <si>
-    <t>amd/Kimi-K2.5-MXFP4</t>
-  </si>
-  <si>
-    <t>kimik2.5</t>
-  </si>
-  <si>
-    <t>fp4</t>
-  </si>
-  <si>
-    <t>rocm/atom-dev:nightly_202603251629</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi355x-atom</t>
-  </si>
-  <si>
-    <t>MiniMaxAI/MiniMax-M2.5</t>
-  </si>
-  <si>
-    <t>minimaxm2.5</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi355x-atom</t>
-  </si>
-  <si>
-    <t>openai/gpt-oss-120b</t>
-  </si>
-  <si>
-    <t>gptoss</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-atom-mtp</t>
-  </si>
-  <si>
-    <t>amd/DeepSeek-R1-0528-MXFP4-MTP-MoEFP4</t>
-  </si>
-  <si>
-    <t>dsr1</t>
-  </si>
-  <si>
-    <t>rocm/atom:rocm7.2.1-ubuntu24.04-pytorch2.9.1-atom0.1.2</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-atom-mtp</t>
-  </si>
-  <si>
-    <t>deepseek-ai/DeepSeek-R1-0528</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-atom</t>
-  </si>
-  <si>
-    <t>amd/DeepSeek-R1-0528-MXFP4-Preview</t>
-  </si>
-  <si>
-    <t>rocm/atom:rocm7.1.1-ubuntu24.04-pytorch2.9-atom0.1.1-MI350x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-atom</t>
-  </si>
-  <si>
-    <t>dsv4-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>sgl-project/DeepSeek-V4-Pro-FP8</t>
-  </si>
-  <si>
-    <t>dsv4</t>
-  </si>
-  <si>
-    <t>sglang</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:rocm720-deepseek-v4-mi35x</t>
-  </si>
-  <si>
-    <t>dsv4-fp4-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>deepseek-ai/DeepSeek-V4-Pro</t>
-  </si>
-  <si>
-    <t>dsv4-fp4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g57</t>
-  </si>
-  <si>
-    <t>vllm</t>
-  </si>
-  <si>
-    <t>rocm/pytorch-private:dsv4_dsv4_adapt_upstream_0430</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>lmsysorg/sglang:v0.5.9-rocm700-mi35x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi300x-sglang</t>
-  </si>
-  <si>
-    <t>mi300x</t>
-  </si>
-  <si>
-    <t>lmsysorg/sglang:v0.5.9-rocm700-mi30x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi325x-sglang</t>
-  </si>
-  <si>
-    <t>mi325x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen3.5-397B-A17B</t>
-  </si>
-  <si>
-    <t>qwen3.5</t>
-  </si>
-  <si>
-    <t>bf16</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260215</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi355x-atom</t>
-  </si>
-  <si>
-    <t>rocm/atom:rocm7.2.1-ubuntu24.04-pytorch2.9.1-atom0.1.2-vllm0.17.0</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi300x-sglang</t>
-  </si>
-  <si>
-    <t>lmsysorg/sglang:v0.5.9-rocm720-mi30x</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi325x-sglang</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi325x-sglang</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen3.5-397B-A17B-FP8</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260218</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi355x-atom</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi300x-sglang</t>
-  </si>
-  <si>
-    <t>glm5-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260219</t>
-  </si>
-  <si>
-    <t>kimik2.5-int4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>moonshotai/Kimi-K2.5</t>
-  </si>
-  <si>
-    <t>mi355x_srok</t>
-  </si>
-  <si>
-    <t>int4</t>
-  </si>
-  <si>
-    <t>aigmkt/kimi-k25-dev</t>
-  </si>
-  <si>
-    <t>kimik2.5-int4-mi325x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.18.0</t>
-  </si>
-  <si>
-    <t>kimik2.5-fp4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g42</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.15.1</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi300x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.16.0</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi325x-vllm</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi300x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.17.0</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi325x-vllm</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>amd/gpt-oss-120b-w-mxfp4-a-fp8</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-sglang-disagg</t>
-  </si>
-  <si>
-    <t>mi355x-disagg</t>
-  </si>
-  <si>
-    <t>sglang-disagg</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:sglang-0.5.9-rocm720-mi35x-mori-0227-2</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-sglang-disagg-mtp</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-sglang-disagg</t>
-  </si>
-  <si>
-    <t>amd/DeepSeek-R1-0528-MXFP4</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:sglang-0.5.9-rocm720-mi35x-mori-0227-3</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-sglang-disagg-mtp</t>
-  </si>
-  <si>
     <t>Ecosystem</t>
   </si>
   <si>
@@ -2042,61 +1847,10 @@
     <t>Cluster Type</t>
   </si>
   <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>mi300x-amd_0, mi300x-amd_1, mi300x-amd_2, mi300x-amd_3, mi300x-amd_4, mi300x-amds_0, mi300x-amds_1, mi300x-amds_2, mi300x-amds_3</t>
-  </si>
-  <si>
-    <t>SLURM</t>
-  </si>
-  <si>
-    <t>mi325x-amd_0, mi325x-amd_1, mi325x-amd_2, mi325x-amd_3</t>
-  </si>
-  <si>
-    <t>Docker/Self-hosted</t>
-  </si>
-  <si>
-    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2, mi355x-amds_3, mi355x-amds_4, mi355x-amds_5, mi355x-amds_6, mi355x-amds_7, mi355x-amds_8, mi355x-amd_p01_g06</t>
-  </si>
-  <si>
-    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2</t>
-  </si>
-  <si>
-    <t>mi355x-m15-17</t>
-  </si>
-  <si>
-    <t>mi355x-amd</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g09</t>
-  </si>
-  <si>
-    <t>mi355x-amd_9</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g17</t>
-  </si>
-  <si>
-    <t>mi355x-amd_17</t>
-  </si>
-  <si>
-    <t>mi355x-amd_42</t>
-  </si>
-  <si>
-    <t>mi355x-tw-sctrl</t>
-  </si>
-  <si>
-    <t>mi355x-amds</t>
-  </si>
-  <si>
     <t>Total AMD Inference Nodes</t>
   </si>
   <si>
-    <t>mi300x: 9  •  mi325x: 4  •  mi355x: 10  •  mi355x-disagg: 3  •  mi355x-m15-17: 1  •  mi355x-p02-g09: 1  •  mi355x-p02-g17: 1  •  mi355x-p02-g42: 1  •  mi355x-tw-sctrl: 1</t>
-  </si>
-  <si>
-    <t>9 GPU pool types</t>
+    <t>0 GPU pool types</t>
   </si>
   <si>
     <t>InferenceMAX CI Workflows — ROCm/InferenceMAX_rocm (.github/workflows/)</t>
@@ -2494,7 +2248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2630,8 +2384,34 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF2E7D32"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000777"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2657,7 +2437,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="47">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2858,12 +2638,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF4E342E"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2882,6 +2656,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF78909C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1565C022"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2895,6 +2675,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2962,7 +2748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3147,31 +2933,61 @@
     <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3180,19 +2996,22 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3201,28 +3020,28 @@
     <xf numFmtId="0" fontId="19" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="44" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="44" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8643,7 +8462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:22" ht="30" customHeight="1">
+    <row r="80" spans="1:22" ht="28" customHeight="1">
       <c r="A80" s="27" t="s">
         <v>227</v>
       </c>
@@ -8685,7 +8504,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1">
+    <row r="82" spans="1:7" ht="28" customHeight="1">
       <c r="A82" s="34" t="s">
         <v>237</v>
       </c>
@@ -8727,7 +8546,7 @@
       </c>
       <c r="G83" s="41"/>
     </row>
-    <row r="84" spans="1:7" ht="40" customHeight="1">
+    <row r="84" spans="1:7" ht="42" customHeight="1">
       <c r="A84" s="42" t="s">
         <v>247</v>
       </c>
@@ -8769,7 +8588,7 @@
       </c>
       <c r="G85" s="49"/>
     </row>
-    <row r="86" spans="1:7" ht="30" customHeight="1">
+    <row r="86" spans="1:7" ht="182" customHeight="1">
       <c r="A86" s="50" t="s">
         <v>7</v>
       </c>
@@ -9483,16 +9302,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="34.7109375" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="80.7109375" customWidth="1"/>
-    <col min="7" max="7" width="29.7109375" customWidth="1"/>
+    <col min="4" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="60.7109375" customWidth="1"/>
+    <col min="7" max="7" width="35.7109375" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" customWidth="1"/>
     <col min="10" max="10" width="42.7109375" customWidth="1"/>
@@ -9530,13 +9348,10 @@
       <c r="E2" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="20" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="B3" s="61">
         <v>273</v>
@@ -9548,33 +9363,30 @@
         <v>69</v>
       </c>
       <c r="E3" s="61" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="B4" s="62">
+        <v>74</v>
+      </c>
+      <c r="C4" s="62">
+        <v>38</v>
+      </c>
+      <c r="D4" s="62">
+        <v>36</v>
+      </c>
+      <c r="E4" s="62" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="20" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="5" spans="1:11" ht="22" customHeight="1">
+      <c r="A5" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="63">
-        <v>74</v>
-      </c>
-      <c r="C4" s="63">
-        <v>38</v>
-      </c>
-      <c r="D4" s="63">
-        <v>36</v>
-      </c>
-      <c r="E4" s="63" t="s">
-        <v>390</v>
-      </c>
-      <c r="F4" s="64" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="22" customHeight="1">
       <c r="B5" s="1">
         <v>347</v>
       </c>
@@ -9585,10 +9397,7 @@
         <v>105</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22" customHeight="1">
@@ -9631,7 +9440,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>382</v>
@@ -9640,25 +9449,25 @@
         <v>288</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F8" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="J8" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="K8" s="15" t="s">
         <v>397</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="K8" s="15" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="20" customHeight="1">
@@ -9666,7 +9475,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>382</v>
@@ -9675,25 +9484,25 @@
         <v>288</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G9" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>399</v>
-      </c>
       <c r="K9" s="15" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="20" customHeight="1">
@@ -9701,7 +9510,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>382</v>
@@ -9710,25 +9519,25 @@
         <v>288</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F10" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="K10" s="15" t="s">
         <v>405</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="20" customHeight="1">
@@ -9736,7 +9545,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>382</v>
@@ -9745,25 +9554,25 @@
         <v>288</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F11" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J11" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="K11" s="15" t="s">
         <v>411</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="20" customHeight="1">
@@ -9771,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>382</v>
@@ -9780,25 +9589,25 @@
         <v>288</v>
       </c>
       <c r="E12" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="H12" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="I12" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="K12" s="15" t="s">
         <v>418</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="20" customHeight="1">
@@ -9806,7 +9615,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>382</v>
@@ -9815,25 +9624,25 @@
         <v>288</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F13" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="K13" s="15" t="s">
         <v>423</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="20" customHeight="1">
@@ -9841,7 +9650,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>382</v>
@@ -9850,25 +9659,25 @@
         <v>288</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F14" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J14" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="K14" s="15" t="s">
         <v>428</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20" customHeight="1">
@@ -9876,7 +9685,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C15" s="15" t="s">
         <v>382</v>
@@ -9885,25 +9694,25 @@
         <v>288</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F15" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="K15" s="15" t="s">
         <v>433</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="20" customHeight="1">
@@ -9911,7 +9720,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>382</v>
@@ -9920,25 +9729,25 @@
         <v>288</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F16" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="K16" s="15" t="s">
         <v>438</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="20" customHeight="1">
@@ -9946,7 +9755,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>382</v>
@@ -9955,25 +9764,25 @@
         <v>288</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="20" customHeight="1">
@@ -9981,7 +9790,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>382</v>
@@ -9990,25 +9799,25 @@
         <v>288</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F18" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="K18" s="15" t="s">
         <v>447</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="20" customHeight="1">
@@ -10016,7 +9825,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>382</v>
@@ -10025,25 +9834,25 @@
         <v>288</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F19" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J19" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="K19" s="15" t="s">
         <v>452</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="20" customHeight="1">
@@ -10051,7 +9860,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>383</v>
@@ -10060,25 +9869,25 @@
         <v>289</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="I20" s="18" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="20" customHeight="1">
@@ -10086,7 +9895,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>383</v>
@@ -10095,25 +9904,25 @@
         <v>289</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="20" customHeight="1">
@@ -10121,7 +9930,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>383</v>
@@ -10130,22 +9939,22 @@
         <v>289</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K22" s="18"/>
     </row>
@@ -10154,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C23" s="18" t="s">
         <v>383</v>
@@ -10163,25 +9972,25 @@
         <v>289</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="20" customHeight="1">
@@ -10198,25 +10007,25 @@
         <v>288</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F24" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="K24" s="15" t="s">
         <v>468</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="20" customHeight="1">
@@ -10230,16 +10039,16 @@
         <v>383</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H25" s="18" t="s">
         <v>22</v>
@@ -10248,10 +10057,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="20" customHeight="1">
@@ -10259,7 +10068,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>382</v>
@@ -10268,25 +10077,25 @@
         <v>288</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F26" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="J26" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="K26" s="15" t="s">
         <v>477</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>478</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>479</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="20" customHeight="1">
@@ -10294,7 +10103,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>382</v>
@@ -10303,25 +10112,25 @@
         <v>288</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F27" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="J27" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="K27" s="15" t="s">
         <v>483</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>485</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="20" customHeight="1">
@@ -10329,7 +10138,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>382</v>
@@ -10338,25 +10147,25 @@
         <v>288</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F28" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="K28" s="15" t="s">
         <v>488</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="20" customHeight="1">
@@ -10364,34 +10173,34 @@
         <v>22</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C29" s="15" t="s">
         <v>382</v>
       </c>
       <c r="D29" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="G29" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="H29" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="K29" s="15" t="s">
         <v>495</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="20" customHeight="1">
@@ -10399,40 +10208,211 @@
         <v>23</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>383</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="F30" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>493</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="K30" s="18" t="s">
         <v>495</v>
       </c>
-      <c r="G30" s="18" t="s">
-        <v>496</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="18" t="s">
+    </row>
+    <row r="33" spans="1:11" ht="26" customHeight="1">
+      <c r="A33" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+    </row>
+    <row r="34" spans="1:11" ht="22" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="K30" s="18" t="s">
-        <v>498</v>
-      </c>
+      <c r="E34" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="30" customHeight="1">
+      <c r="A35" s="63" t="s">
+        <v>322</v>
+      </c>
+      <c r="B35" s="64" t="s">
+        <v>503</v>
+      </c>
+      <c r="C35" s="65">
+        <v>182</v>
+      </c>
+      <c r="D35" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="E35" s="66" t="s">
+        <v>230</v>
+      </c>
+      <c r="F35" s="64" t="s">
+        <v>504</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="30" customHeight="1">
+      <c r="A36" s="63"/>
+      <c r="B36" s="64" t="s">
+        <v>506</v>
+      </c>
+      <c r="C36" s="65">
+        <v>159</v>
+      </c>
+      <c r="D36" s="66" t="s">
+        <v>507</v>
+      </c>
+      <c r="E36" s="68" t="s">
+        <v>508</v>
+      </c>
+      <c r="F36" s="64" t="s">
+        <v>509</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="22" customHeight="1">
+      <c r="A37" s="63"/>
+      <c r="B37" s="38" t="s">
+        <v>511</v>
+      </c>
+      <c r="C37" s="69">
+        <v>341</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="F37" s="41" t="s">
+        <v>513</v>
+      </c>
+      <c r="G37" s="40" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="30" customHeight="1">
+      <c r="A38" s="70" t="s">
+        <v>352</v>
+      </c>
+      <c r="B38" s="71" t="s">
+        <v>515</v>
+      </c>
+      <c r="C38" s="72">
+        <v>84</v>
+      </c>
+      <c r="D38" s="73" t="s">
+        <v>516</v>
+      </c>
+      <c r="E38" s="74" t="s">
+        <v>517</v>
+      </c>
+      <c r="F38" s="71" t="s">
+        <v>518</v>
+      </c>
+      <c r="G38" s="75" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="22" customHeight="1">
+      <c r="A39" s="70"/>
+      <c r="B39" s="46" t="s">
+        <v>520</v>
+      </c>
+      <c r="C39" s="76">
+        <v>84</v>
+      </c>
+      <c r="D39" s="48" t="s">
+        <v>521</v>
+      </c>
+      <c r="E39" s="77" t="s">
+        <v>522</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>523</v>
+      </c>
+      <c r="G39" s="48" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="26" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="26">
+        <v>341</v>
+      </c>
+      <c r="D40" s="78" t="s">
+        <v>526</v>
+      </c>
+      <c r="E40" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="F40" s="78" t="s">
+        <v>528</v>
+      </c>
+      <c r="G40" s="78"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:K30"/>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="F40:G40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10470,22 +10450,22 @@
         <v>271</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>502</v>
+        <v>530</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>505</v>
+        <v>533</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -10502,28 +10482,28 @@
         <v>324</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="F2" s="59" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
       <c r="G2" s="59" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H2" s="59" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
       <c r="I2" s="59" t="s">
         <v>331</v>
       </c>
       <c r="J2" s="59" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="K2" s="59" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="28" customHeight="1">
@@ -10537,25 +10517,25 @@
         <v>335</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="G3" s="59" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H3" s="59" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="I3" s="59" t="s">
         <v>341</v>
       </c>
       <c r="J3" s="59" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="K3" s="59"/>
     </row>
@@ -10570,28 +10550,28 @@
         <v>335</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H4" s="59" t="s">
-        <v>517</v>
+        <v>545</v>
       </c>
       <c r="I4" s="59" t="s">
         <v>341</v>
       </c>
       <c r="J4" s="59" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="K4" s="59" t="s">
-        <v>518</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="28" customHeight="1">
@@ -10605,25 +10585,25 @@
         <v>335</v>
       </c>
       <c r="D5" s="59" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="G5" s="59" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H5" s="59" t="s">
-        <v>519</v>
+        <v>547</v>
       </c>
       <c r="I5" s="59" t="s">
         <v>341</v>
       </c>
       <c r="J5" s="59" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="K5" s="59"/>
     </row>
@@ -10638,25 +10618,25 @@
         <v>335</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>515</v>
+        <v>543</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="I6" s="59" t="s">
         <v>341</v>
       </c>
       <c r="J6" s="59" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="K6" s="59" t="s">
         <v>351</v>
@@ -10673,19 +10653,19 @@
         <v>354</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>168</v>
@@ -10708,19 +10688,19 @@
         <v>354</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>168</v>
@@ -10743,19 +10723,19 @@
         <v>354</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>521</v>
+        <v>549</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>168</v>
@@ -10778,19 +10758,19 @@
         <v>354</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>524</v>
+        <v>552</v>
       </c>
       <c r="F10" s="25" t="s">
-        <v>522</v>
+        <v>550</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>168</v>
@@ -10810,1021 +10790,56 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="60.7109375" customWidth="1"/>
+    <col min="4" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="65" t="s">
-        <v>525</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="79" t="s">
+        <v>553</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="65" t="s">
-        <v>526</v>
-      </c>
-      <c r="B2" s="65" t="s">
-        <v>527</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>528</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>529</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>530</v>
-      </c>
-      <c r="F2" s="65" t="s">
+      <c r="A2" s="79" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>555</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>556</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>557</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>558</v>
+      </c>
+      <c r="F2" s="79" t="s">
         <v>311</v>
       </c>
-      <c r="G2" s="65" t="s">
-        <v>531</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16" customHeight="1">
-      <c r="A3" s="20" t="s">
-        <v>533</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>534</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G3" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16" customHeight="1">
-      <c r="A5" s="20" t="s">
-        <v>545</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G5" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16" customHeight="1">
-      <c r="A6" s="20" t="s">
-        <v>548</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G6" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>552</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G7" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G8" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G9" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="20" t="s">
+      <c r="G2" s="79" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="16" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="H2" s="79" t="s">
         <v>560</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G10" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16" customHeight="1">
-      <c r="A11" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>562</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>563</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G11" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16" customHeight="1">
-      <c r="A12" s="20" t="s">
-        <v>566</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>563</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G12" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="20" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16" customHeight="1">
-      <c r="A13" s="20" t="s">
-        <v>568</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>567</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>563</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>569</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G13" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16" customHeight="1">
-      <c r="A14" s="20" t="s">
-        <v>572</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G14" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16" customHeight="1">
-      <c r="A15" s="20" t="s">
-        <v>574</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G15" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16" customHeight="1">
-      <c r="A16" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G16" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="16" customHeight="1">
-      <c r="A17" s="20" t="s">
-        <v>579</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G17" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="16" customHeight="1">
-      <c r="A18" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G18" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="16" customHeight="1">
-      <c r="A19" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G19" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="16" customHeight="1">
-      <c r="A20" s="20" t="s">
-        <v>587</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G20" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="16" customHeight="1">
-      <c r="A21" s="20" t="s">
-        <v>589</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>581</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G21" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16" customHeight="1">
-      <c r="A22" s="20" t="s">
-        <v>590</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G22" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="16" customHeight="1">
-      <c r="A23" s="20" t="s">
-        <v>592</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G23" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="16" customHeight="1">
-      <c r="A24" s="20" t="s">
-        <v>594</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="G24" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="16" customHeight="1">
-      <c r="A25" s="20" t="s">
-        <v>595</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>591</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G25" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16" customHeight="1">
-      <c r="A26" s="20" t="s">
-        <v>596</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>534</v>
-      </c>
-      <c r="C26" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>564</v>
-      </c>
-      <c r="G26" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H26" s="20" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="16" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>598</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>599</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>600</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G27" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="16" customHeight="1">
-      <c r="A28" s="20" t="s">
-        <v>603</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>599</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G28" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H28" s="20" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="16" customHeight="1">
-      <c r="A29" s="20" t="s">
-        <v>605</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>606</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G29" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="16" customHeight="1">
-      <c r="A30" s="20" t="s">
-        <v>607</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G30" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H30" s="20" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="16" customHeight="1">
-      <c r="A31" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G31" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="16" customHeight="1">
-      <c r="A32" s="20" t="s">
-        <v>611</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>547</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G32" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H32" s="20" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="16" customHeight="1">
-      <c r="A33" s="20" t="s">
-        <v>612</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>575</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G33" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="16" customHeight="1">
-      <c r="A34" s="20" t="s">
-        <v>614</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>549</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G34" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="16" customHeight="1">
-      <c r="A35" s="20" t="s">
-        <v>615</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>550</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>570</v>
-      </c>
-      <c r="G35" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="16" customHeight="1">
-      <c r="A36" s="20" t="s">
-        <v>617</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="20" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="16" customHeight="1">
-      <c r="A37" s="20" t="s">
-        <v>621</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="16" customHeight="1">
-      <c r="A38" s="20" t="s">
-        <v>622</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>623</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="20" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="16" customHeight="1">
-      <c r="A39" s="20" t="s">
-        <v>625</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>623</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>619</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>624</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H39"/>
+  <autoFilter ref="A2:H3"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -11834,7 +10849,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -11845,194 +10860,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26" customHeight="1">
-      <c r="A1" s="67" t="s">
-        <v>626</v>
-      </c>
-      <c r="B1" s="67" t="s">
-        <v>627</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>628</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>629</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="20" customHeight="1">
-      <c r="A2" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B2" s="68" t="s">
-        <v>575</v>
-      </c>
-      <c r="C2" s="69" t="s">
-        <v>632</v>
-      </c>
-      <c r="D2" s="70">
-        <v>9</v>
-      </c>
-      <c r="E2" s="68" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="20" customHeight="1">
-      <c r="A3" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B3" s="68" t="s">
-        <v>578</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>634</v>
-      </c>
-      <c r="D3" s="70">
-        <v>4</v>
-      </c>
-      <c r="E3" s="68" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="20" customHeight="1">
-      <c r="A4" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>536</v>
-      </c>
-      <c r="C4" s="69" t="s">
-        <v>636</v>
-      </c>
-      <c r="D4" s="70">
-        <v>10</v>
-      </c>
-      <c r="E4" s="68" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="20" customHeight="1">
-      <c r="A5" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>618</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>637</v>
-      </c>
-      <c r="D5" s="70">
-        <v>3</v>
-      </c>
-      <c r="E5" s="68" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1">
-      <c r="A6" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>638</v>
-      </c>
-      <c r="C6" s="69" t="s">
-        <v>639</v>
-      </c>
-      <c r="D6" s="70">
-        <v>1</v>
-      </c>
-      <c r="E6" s="68" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1">
-      <c r="A7" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>640</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>641</v>
-      </c>
-      <c r="D7" s="70">
-        <v>1</v>
-      </c>
-      <c r="E7" s="68" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1">
-      <c r="A8" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B8" s="68" t="s">
-        <v>642</v>
-      </c>
-      <c r="C8" s="69" t="s">
-        <v>643</v>
-      </c>
-      <c r="D8" s="70">
-        <v>1</v>
-      </c>
-      <c r="E8" s="68" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="20" customHeight="1">
-      <c r="A9" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>606</v>
-      </c>
-      <c r="C9" s="69" t="s">
-        <v>644</v>
-      </c>
-      <c r="D9" s="70">
-        <v>1</v>
-      </c>
-      <c r="E9" s="68" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="20" customHeight="1">
-      <c r="A10" s="68" t="s">
-        <v>631</v>
-      </c>
-      <c r="B10" s="68" t="s">
-        <v>645</v>
-      </c>
-      <c r="C10" s="69" t="s">
-        <v>646</v>
-      </c>
-      <c r="D10" s="70">
-        <v>1</v>
-      </c>
-      <c r="E10" s="68" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="28" customHeight="1">
-      <c r="A11" s="71" t="s">
-        <v>647</v>
-      </c>
-      <c r="B11" s="71"/>
-      <c r="C11" s="72" t="s">
-        <v>648</v>
-      </c>
-      <c r="D11" s="71">
-        <v>31</v>
-      </c>
-      <c r="E11" s="71" t="s">
-        <v>649</v>
+      <c r="A1" s="80" t="s">
+        <v>561</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>562</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>563</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>564</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28" customHeight="1">
+      <c r="A2" s="81" t="s">
+        <v>566</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="81">
+        <v>0</v>
+      </c>
+      <c r="E2" s="81" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E2"/>
   <mergeCells count="1">
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12049,327 +10909,327 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="65" t="s">
-        <v>650</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="79" t="s">
+        <v>568</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
-      <c r="A2" s="65" t="s">
-        <v>651</v>
-      </c>
-      <c r="B2" s="65" t="s">
-        <v>652</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>653</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>654</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>655</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>656</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>657</v>
-      </c>
-      <c r="H2" s="65" t="s">
+      <c r="A2" s="79" t="s">
+        <v>569</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>570</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>572</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>573</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>574</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2" s="79" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="182" customHeight="1">
-      <c r="A3" s="73" t="s">
-        <v>658</v>
+      <c r="A3" s="83" t="s">
+        <v>576</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>659</v>
-      </c>
-      <c r="C3" s="74" t="s">
-        <v>660</v>
+        <v>577</v>
+      </c>
+      <c r="C3" s="84" t="s">
+        <v>578</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>661</v>
+        <v>579</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>662</v>
+        <v>580</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>663</v>
+        <v>581</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>664</v>
+        <v>582</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>665</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1">
-      <c r="A4" s="73" t="s">
-        <v>666</v>
+      <c r="A4" s="83" t="s">
+        <v>584</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>667</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>668</v>
+        <v>585</v>
+      </c>
+      <c r="C4" s="84" t="s">
+        <v>586</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>669</v>
+        <v>587</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>670</v>
+        <v>588</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>671</v>
+        <v>589</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>672</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1">
-      <c r="A5" s="73" t="s">
-        <v>673</v>
+      <c r="A5" s="83" t="s">
+        <v>591</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>674</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>668</v>
+        <v>592</v>
+      </c>
+      <c r="C5" s="84" t="s">
+        <v>586</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>669</v>
+        <v>587</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>675</v>
+        <v>593</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>671</v>
+        <v>589</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>676</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="84" customHeight="1">
-      <c r="A6" s="73" t="s">
-        <v>671</v>
+      <c r="A6" s="83" t="s">
+        <v>589</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>678</v>
+        <v>595</v>
+      </c>
+      <c r="C6" s="84" t="s">
+        <v>596</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>679</v>
+        <v>597</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>680</v>
+        <v>598</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>664</v>
+        <v>582</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>681</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1">
-      <c r="A7" s="73" t="s">
-        <v>682</v>
+      <c r="A7" s="83" t="s">
+        <v>600</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>683</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>684</v>
+        <v>601</v>
+      </c>
+      <c r="C7" s="84" t="s">
+        <v>602</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>685</v>
+        <v>603</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>686</v>
+        <v>604</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>687</v>
+        <v>605</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>688</v>
+        <v>606</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>689</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" customHeight="1">
-      <c r="A8" s="73" t="s">
-        <v>690</v>
+      <c r="A8" s="83" t="s">
+        <v>608</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>692</v>
+        <v>609</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>610</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>693</v>
+        <v>611</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>694</v>
+        <v>612</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>695</v>
+        <v>613</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>696</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" customHeight="1">
-      <c r="A9" s="73" t="s">
-        <v>697</v>
+      <c r="A9" s="83" t="s">
+        <v>615</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="C9" s="74" t="s">
-        <v>699</v>
+        <v>616</v>
+      </c>
+      <c r="C9" s="84" t="s">
+        <v>617</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>700</v>
+        <v>618</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>701</v>
+        <v>619</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>702</v>
+        <v>620</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>703</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1">
-      <c r="A10" s="75" t="s">
-        <v>704</v>
-      </c>
-      <c r="B10" s="76" t="s">
-        <v>705</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>706</v>
-      </c>
-      <c r="D10" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="76" t="s">
-        <v>707</v>
-      </c>
-      <c r="F10" s="76" t="s">
-        <v>708</v>
-      </c>
-      <c r="G10" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="76" t="s">
-        <v>709</v>
+      <c r="A10" s="85" t="s">
+        <v>622</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>623</v>
+      </c>
+      <c r="C10" s="84" t="s">
+        <v>624</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="86" t="s">
+        <v>625</v>
+      </c>
+      <c r="F10" s="86" t="s">
+        <v>626</v>
+      </c>
+      <c r="G10" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="86" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1">
-      <c r="A11" s="75" t="s">
-        <v>710</v>
-      </c>
-      <c r="B11" s="76" t="s">
-        <v>711</v>
-      </c>
-      <c r="C11" s="74" t="s">
-        <v>706</v>
-      </c>
-      <c r="D11" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="76" t="s">
-        <v>712</v>
-      </c>
-      <c r="F11" s="76" t="s">
-        <v>713</v>
-      </c>
-      <c r="G11" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>714</v>
+      <c r="A11" s="85" t="s">
+        <v>628</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>629</v>
+      </c>
+      <c r="C11" s="84" t="s">
+        <v>624</v>
+      </c>
+      <c r="D11" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="86" t="s">
+        <v>630</v>
+      </c>
+      <c r="F11" s="86" t="s">
+        <v>631</v>
+      </c>
+      <c r="G11" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="86" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1">
-      <c r="A12" s="75" t="s">
-        <v>715</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>716</v>
-      </c>
-      <c r="C12" s="74" t="s">
-        <v>717</v>
-      </c>
-      <c r="D12" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="76" t="s">
-        <v>718</v>
-      </c>
-      <c r="F12" s="76" t="s">
-        <v>719</v>
-      </c>
-      <c r="G12" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="76" t="s">
-        <v>720</v>
+      <c r="A12" s="85" t="s">
+        <v>633</v>
+      </c>
+      <c r="B12" s="86" t="s">
+        <v>634</v>
+      </c>
+      <c r="C12" s="84" t="s">
+        <v>635</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="86" t="s">
+        <v>636</v>
+      </c>
+      <c r="F12" s="86" t="s">
+        <v>637</v>
+      </c>
+      <c r="G12" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="86" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1">
-      <c r="A13" s="75" t="s">
-        <v>721</v>
-      </c>
-      <c r="B13" s="76" t="s">
-        <v>722</v>
-      </c>
-      <c r="C13" s="74" t="s">
-        <v>723</v>
-      </c>
-      <c r="D13" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="76" t="s">
-        <v>724</v>
-      </c>
-      <c r="F13" s="76" t="s">
-        <v>725</v>
-      </c>
-      <c r="G13" s="76" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>726</v>
+      <c r="A13" s="85" t="s">
+        <v>639</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>640</v>
+      </c>
+      <c r="C13" s="84" t="s">
+        <v>641</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="86" t="s">
+        <v>642</v>
+      </c>
+      <c r="F13" s="86" t="s">
+        <v>643</v>
+      </c>
+      <c r="G13" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="86" t="s">
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -12384,7 +11244,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
-    <tabColor rgb="FF37474F"/>
+    <tabColor rgb="FF78909C"/>
   </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12395,172 +11255,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
-      <c r="A1" s="26" t="s">
-        <v>727</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
+      <c r="A1" s="87" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
-      <c r="A2" s="26" t="s">
-        <v>728</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>729</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1">
-      <c r="A3" s="77" t="s">
-        <v>731</v>
-      </c>
-      <c r="B3" s="78" t="s">
-        <v>732</v>
-      </c>
-      <c r="C3" s="79" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="22" customHeight="1">
-      <c r="A4" s="80" t="s">
-        <v>734</v>
-      </c>
-      <c r="B4" s="79" t="s">
-        <v>735</v>
-      </c>
-      <c r="C4" s="79" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="22" customHeight="1">
-      <c r="A5" s="80" t="s">
-        <v>737</v>
-      </c>
-      <c r="B5" s="79" t="s">
-        <v>738</v>
-      </c>
-      <c r="C5" s="79" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="22" customHeight="1">
-      <c r="A6" s="80" t="s">
-        <v>740</v>
-      </c>
-      <c r="B6" s="79" t="s">
-        <v>741</v>
-      </c>
-      <c r="C6" s="79" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="22" customHeight="1">
-      <c r="A7" s="80" t="s">
-        <v>743</v>
-      </c>
-      <c r="B7" s="79" t="s">
-        <v>744</v>
-      </c>
-      <c r="C7" s="79" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="22" customHeight="1">
-      <c r="A8" s="80" t="s">
-        <v>746</v>
-      </c>
-      <c r="B8" s="79" t="s">
-        <v>747</v>
-      </c>
-      <c r="C8" s="79" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="22" customHeight="1">
-      <c r="A9" s="80" t="s">
-        <v>749</v>
-      </c>
-      <c r="B9" s="79" t="s">
-        <v>750</v>
-      </c>
-      <c r="C9" s="79" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="22" customHeight="1">
-      <c r="A10" s="80" t="s">
-        <v>752</v>
-      </c>
-      <c r="B10" s="79" t="s">
-        <v>753</v>
-      </c>
-      <c r="C10" s="79" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="22" customHeight="1">
-      <c r="A11" s="81" t="s">
-        <v>755</v>
-      </c>
-      <c r="B11" s="82" t="s">
-        <v>756</v>
-      </c>
-      <c r="C11" s="79" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="22" customHeight="1">
-      <c r="A12" s="83" t="s">
-        <v>755</v>
-      </c>
-      <c r="B12" s="84" t="s">
-        <v>758</v>
-      </c>
-      <c r="C12" s="79" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="22" customHeight="1">
-      <c r="A13" s="85" t="s">
-        <v>760</v>
-      </c>
-      <c r="B13" s="86" t="s">
-        <v>761</v>
-      </c>
-      <c r="C13" s="79" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="22" customHeight="1">
-      <c r="A14" s="80" t="s">
-        <v>763</v>
-      </c>
-      <c r="B14" s="79" t="s">
-        <v>764</v>
-      </c>
-      <c r="C14" s="79" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="22" customHeight="1">
-      <c r="A15" s="80" t="s">
-        <v>766</v>
-      </c>
-      <c r="B15" s="79" t="s">
-        <v>767</v>
-      </c>
-      <c r="C15" s="87" t="s">
+      <c r="A2" s="87" t="s">
+        <v>646</v>
+      </c>
+      <c r="B2" s="87" t="s">
+        <v>647</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="20" customHeight="1">
+      <c r="A3" s="88" t="s">
+        <v>649</v>
+      </c>
+      <c r="B3" s="89" t="s">
+        <v>650</v>
+      </c>
+      <c r="C3" s="90" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="20" customHeight="1">
+      <c r="A4" s="91" t="s">
+        <v>652</v>
+      </c>
+      <c r="B4" s="90" t="s">
+        <v>653</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="20" customHeight="1">
+      <c r="A5" s="91" t="s">
+        <v>655</v>
+      </c>
+      <c r="B5" s="90" t="s">
+        <v>656</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="20" customHeight="1">
+      <c r="A6" s="91" t="s">
+        <v>658</v>
+      </c>
+      <c r="B6" s="90" t="s">
+        <v>659</v>
+      </c>
+      <c r="C6" s="90" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20" customHeight="1">
+      <c r="A7" s="91" t="s">
+        <v>661</v>
+      </c>
+      <c r="B7" s="90" t="s">
+        <v>662</v>
+      </c>
+      <c r="C7" s="90" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20" customHeight="1">
+      <c r="A8" s="91" t="s">
+        <v>664</v>
+      </c>
+      <c r="B8" s="90" t="s">
+        <v>665</v>
+      </c>
+      <c r="C8" s="90" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20" customHeight="1">
+      <c r="A9" s="91" t="s">
+        <v>667</v>
+      </c>
+      <c r="B9" s="90" t="s">
+        <v>668</v>
+      </c>
+      <c r="C9" s="90" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20" customHeight="1">
+      <c r="A10" s="91" t="s">
+        <v>670</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>671</v>
+      </c>
+      <c r="C10" s="90" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20" customHeight="1">
+      <c r="A11" s="92" t="s">
+        <v>673</v>
+      </c>
+      <c r="B11" s="93" t="s">
+        <v>674</v>
+      </c>
+      <c r="C11" s="90" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="20" customHeight="1">
+      <c r="A12" s="94" t="s">
+        <v>673</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>676</v>
+      </c>
+      <c r="C12" s="90" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1">
+      <c r="A13" s="96" t="s">
+        <v>678</v>
+      </c>
+      <c r="B13" s="97" t="s">
+        <v>679</v>
+      </c>
+      <c r="C13" s="90" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20" customHeight="1">
+      <c r="A14" s="91" t="s">
+        <v>681</v>
+      </c>
+      <c r="B14" s="90" t="s">
+        <v>682</v>
+      </c>
+      <c r="C14" s="90" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20" customHeight="1">
+      <c r="A15" s="91" t="s">
+        <v>684</v>
+      </c>
+      <c r="B15" s="90" t="s">
+        <v>685</v>
+      </c>
+      <c r="C15" s="98" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1">
-      <c r="A16" s="87" t="s">
-        <v>768</v>
-      </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="87"/>
+      <c r="A16" s="98" t="s">
+        <v>686</v>
+      </c>
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -20,9 +20,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Component CI Matrix'!$A$2:$V$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Framework Detail'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'InferenceMAX Workflows'!$A$2:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Runner Inventory'!$A$7:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wheel Artifact Publishing'!$A$1:$K$10</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="817">
   <si>
     <t>Category</t>
   </si>
@@ -1832,6 +1832,285 @@
     <t>Pinned Docker Image</t>
   </si>
   <si>
+    <t>glm5-fp8-mi355x-atom</t>
+  </si>
+  <si>
+    <t>zai-org/GLM-5-FP8</t>
+  </si>
+  <si>
+    <t>glm5</t>
+  </si>
+  <si>
+    <t>mi355x</t>
+  </si>
+  <si>
+    <t>fp8</t>
+  </si>
+  <si>
+    <t>atom</t>
+  </si>
+  <si>
+    <t>rocm/atom-dev:nightly_202603291522</t>
+  </si>
+  <si>
+    <t>kimik2.5-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>amd/Kimi-K2.5-MXFP4</t>
+  </si>
+  <si>
+    <t>kimik2.5</t>
+  </si>
+  <si>
+    <t>fp4</t>
+  </si>
+  <si>
+    <t>rocm/atom-dev:nightly_202603251629</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi355x-atom</t>
+  </si>
+  <si>
+    <t>MiniMaxAI/MiniMax-M2.5</t>
+  </si>
+  <si>
+    <t>minimaxm2.5</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>openai/gpt-oss-120b</t>
+  </si>
+  <si>
+    <t>gptoss</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-atom-mtp</t>
+  </si>
+  <si>
+    <t>amd/DeepSeek-R1-0528-MXFP4-MTP-MoEFP4</t>
+  </si>
+  <si>
+    <t>dsr1</t>
+  </si>
+  <si>
+    <t>rocm/atom:rocm7.2.1-ubuntu24.04-pytorch2.9.1-atom0.1.2</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-atom-mtp</t>
+  </si>
+  <si>
+    <t>deepseek-ai/DeepSeek-R1-0528</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>amd/DeepSeek-R1-0528-MXFP4-Preview</t>
+  </si>
+  <si>
+    <t>rocm/atom:rocm7.1.1-ubuntu24.04-pytorch2.9-atom0.1.1-MI350x</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-atom</t>
+  </si>
+  <si>
+    <t>dsv4-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>sgl-project/DeepSeek-V4-Pro-FP8</t>
+  </si>
+  <si>
+    <t>dsv4</t>
+  </si>
+  <si>
+    <t>sglang</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:rocm720-deepseek-v4-mi35x</t>
+  </si>
+  <si>
+    <t>dsv4-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>deepseek-ai/DeepSeek-V4-Pro</t>
+  </si>
+  <si>
+    <t>dsv4-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>mi355x-p02-g57</t>
+  </si>
+  <si>
+    <t>vllm</t>
+  </si>
+  <si>
+    <t>rocm/pytorch-private:dsv4_dsv4_adapt_upstream_0430</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.9-rocm700-mi35x</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi300x-sglang</t>
+  </si>
+  <si>
+    <t>mi300x</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.9-rocm700-mi30x</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>mi325x</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen3.5-397B-A17B</t>
+  </si>
+  <si>
+    <t>qwen3.5</t>
+  </si>
+  <si>
+    <t>bf16</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260215</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi355x-atom</t>
+  </si>
+  <si>
+    <t>rocm/atom:rocm7.2.1-ubuntu24.04-pytorch2.9.1-atom0.1.2-vllm0.17.0</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi300x-sglang</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.9-rocm720-mi30x</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen3.5-397B-A17B-FP8</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260218</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-atom</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi300x-sglang</t>
+  </si>
+  <si>
+    <t>glm5-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260219</t>
+  </si>
+  <si>
+    <t>kimik2.5-int4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>moonshotai/Kimi-K2.5</t>
+  </si>
+  <si>
+    <t>mi355x_srok</t>
+  </si>
+  <si>
+    <t>int4</t>
+  </si>
+  <si>
+    <t>aigmkt/kimi-k25-dev</t>
+  </si>
+  <si>
+    <t>kimik2.5-int4-mi325x-vllm</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:v0.18.0</t>
+  </si>
+  <si>
+    <t>kimik2.5-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>mi355x-p02-g42</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:v0.15.1</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi300x-vllm</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:v0.16.0</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi325x-vllm</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi300x-vllm</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:v0.17.0</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi325x-vllm</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>amd/gpt-oss-120b-w-mxfp4-a-fp8</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-sglang-disagg</t>
+  </si>
+  <si>
+    <t>mi355x-disagg</t>
+  </si>
+  <si>
+    <t>sglang-disagg</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:sglang-0.5.9-rocm720-mi35x-mori-0227-2</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-sglang-disagg-mtp</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-sglang-disagg</t>
+  </si>
+  <si>
+    <t>amd/DeepSeek-R1-0528-MXFP4</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:sglang-0.5.9-rocm720-mi35x-mori-0227-3</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-sglang-disagg-mtp</t>
+  </si>
+  <si>
     <t>Ecosystem</t>
   </si>
   <si>
@@ -1847,10 +2126,121 @@
     <t>Cluster Type</t>
   </si>
   <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>b200</t>
+  </si>
+  <si>
+    <t>b200-dgxc_1, b200-dgxc_2, b200-nb_0, b200-nb_1, b200-dgxc-slurm_0, b200-dgxc-slurm_1, b200-dgxc-slurm_2, b200-dgxc-slurm_3, b200-dgxc-slurm_4, b200-dgxc-slurm_5, b200-dgxc-slurm_6, b200-dgxc-slurm_7, b200-dgxc-slurm_8</t>
+  </si>
+  <si>
+    <t>SLURM</t>
+  </si>
+  <si>
+    <t>b200-multinode</t>
+  </si>
+  <si>
+    <t>b200-dgxc-slurm_6, b200-dgxc-slurm_7, b200-dgxc-slurm_8</t>
+  </si>
+  <si>
+    <t>b200-trt</t>
+  </si>
+  <si>
+    <t>b200-nb_0, b200-nb_1</t>
+  </si>
+  <si>
+    <t>Docker/Self-hosted</t>
+  </si>
+  <si>
+    <t>b300</t>
+  </si>
+  <si>
+    <t>b300-nv_0, b300-nv_1, b300-nv_2</t>
+  </si>
+  <si>
+    <t>gb200</t>
+  </si>
+  <si>
+    <t>gb200-nv_0, gb200-nv_1, gb200-nv_2</t>
+  </si>
+  <si>
+    <t>gb300</t>
+  </si>
+  <si>
+    <t>gb300-nv_0, gb300-nv_1, gb300-nv_2</t>
+  </si>
+  <si>
+    <t>h100</t>
+  </si>
+  <si>
+    <t>h100-cr_0, h100-cr_1, h100-cw_0, h100-cw_1, h100-dgxc-slurm_0, h100-dgxc-slurm_1, h100-dgxc-slurm_2, h100-dgxc-slurm_3, h100-dgxc-slurm_4, h100-dgxc-slurm_5, h100-dgxc-slurm_6, h100-dgxc-slurm_7, h100-dgxc-slurm_8, h100-dgxc-slurm_9, h100-dgxc-slurm_10, h100-dgxc-slurm_11</t>
+  </si>
+  <si>
+    <t>h100-multinode</t>
+  </si>
+  <si>
+    <t>h100-dgxc-slurm_9, h100-dgxc-slurm_10, h100-dgxc-slurm_11</t>
+  </si>
+  <si>
+    <t>h200</t>
+  </si>
+  <si>
+    <t>h200-cw_2, h200-cw_3, h200-nb_0, h200-nb_1, h200-dgxc-slurm_0, h200-dgxc-slurm_1, h200-dgxc-slurm_2, h200-dgxc-slurm_3, h200-dgxc-slurm_4, h200-dgxc-slurm_5, h200-dgxc-slurm_6, h200-dgxc-slurm_7, h200-dgxc-slurm_8, h200-dgxc-slurm_9, h200-dgxc-slurm_10, h200-dgxc-slurm_11, h200-dgxc-slurm_12, h200-dgxc-slurm_13</t>
+  </si>
+  <si>
+    <t>h200-multinode</t>
+  </si>
+  <si>
+    <t>h200-dgxc-slurm_11, h200-dgxc-slurm_12, h200-dgxc-slurm_13</t>
+  </si>
+  <si>
+    <t>mi300x-amd_0, mi300x-amd_1, mi300x-amd_2, mi300x-amd_3, mi300x-amd_4, mi300x-amds_0, mi300x-amds_1, mi300x-amds_2, mi300x-amds_3</t>
+  </si>
+  <si>
+    <t>mi325x-amd_0, mi325x-amd_1, mi325x-amd_2, mi325x-amd_3</t>
+  </si>
+  <si>
+    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2, mi355x-amds_3, mi355x-amds_4, mi355x-amds_5, mi355x-amds_6, mi355x-amds_7, mi355x-amds_8, mi355x-amd_p01_g06</t>
+  </si>
+  <si>
+    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2</t>
+  </si>
+  <si>
+    <t>mi355x-m15-17</t>
+  </si>
+  <si>
+    <t>mi355x-amd</t>
+  </si>
+  <si>
+    <t>mi355x-p02-g09</t>
+  </si>
+  <si>
+    <t>mi355x-amd_9</t>
+  </si>
+  <si>
+    <t>mi355x-p02-g17</t>
+  </si>
+  <si>
+    <t>mi355x-amd_17</t>
+  </si>
+  <si>
+    <t>mi355x-amd_42</t>
+  </si>
+  <si>
+    <t>mi355x-tw-sctrl</t>
+  </si>
+  <si>
+    <t>mi355x-amds</t>
+  </si>
+  <si>
     <t>Total AMD Inference Nodes</t>
   </si>
   <si>
-    <t>0 GPU pool types</t>
+    <t>b200: 13  •  b200-multinode: 3  •  b200-trt: 2  •  b300: 3  •  gb200: 3  •  gb300: 3  •  h100: 16  •  h100-multinode: 3  •  h200: 18  •  h200-multinode: 3  •  mi300x: 9  •  mi325x: 4  •  mi355x: 10  •  mi355x-disagg: 3  •  mi355x-m15-17: 1  •  mi355x-p02-g09: 1  •  mi355x-p02-g17: 1  •  mi355x-p02-g42: 1  •  mi355x-tw-sctrl: 1</t>
+  </si>
+  <si>
+    <t>19 GPU pool types</t>
   </si>
   <si>
     <t>InferenceMAX CI Workflows — ROCm/InferenceMAX_rocm (.github/workflows/)</t>
@@ -2248,7 +2638,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2412,6 +2802,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2638,6 +3035,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF4E342E"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2675,12 +3078,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2748,7 +3145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2987,7 +3384,19 @@
     <xf numFmtId="0" fontId="1" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2996,52 +3405,52 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="40" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="44" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="47" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10790,14 +11199,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
@@ -10838,8 +11250,970 @@
         <v>560</v>
       </c>
     </row>
+    <row r="3" spans="1:8" ht="20" customHeight="1">
+      <c r="A3" s="20" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G3" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="20" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G4" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G5" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20" customHeight="1">
+      <c r="A6" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G6" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20" customHeight="1">
+      <c r="A7" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G7" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20" customHeight="1">
+      <c r="A8" s="20" t="s">
+        <v>583</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G8" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20" customHeight="1">
+      <c r="A9" s="20" t="s">
+        <v>585</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G9" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20" customHeight="1">
+      <c r="A10" s="20" t="s">
+        <v>588</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G10" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20" customHeight="1">
+      <c r="A11" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>590</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G11" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20" customHeight="1">
+      <c r="A12" s="20" t="s">
+        <v>594</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G12" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20" customHeight="1">
+      <c r="A13" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>595</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>597</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G13" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20" customHeight="1">
+      <c r="A14" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>586</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G14" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20" customHeight="1">
+      <c r="A15" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G15" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20" customHeight="1">
+      <c r="A16" s="20" t="s">
+        <v>605</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G16" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="20" customHeight="1">
+      <c r="A17" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G17" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="20" customHeight="1">
+      <c r="A18" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G18" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="20" customHeight="1">
+      <c r="A19" s="20" t="s">
+        <v>613</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="20" customHeight="1">
+      <c r="A20" s="20" t="s">
+        <v>615</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G20" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="20" customHeight="1">
+      <c r="A21" s="20" t="s">
+        <v>617</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>611</v>
+      </c>
+      <c r="F21" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G21" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="20" customHeight="1">
+      <c r="A22" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G22" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="20" customHeight="1">
+      <c r="A23" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G23" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="20" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="G24" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="20" customHeight="1">
+      <c r="A25" s="20" t="s">
+        <v>623</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>619</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>610</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G25" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="20" customHeight="1">
+      <c r="A26" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>562</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>563</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="G26" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="20" customHeight="1">
+      <c r="A27" s="20" t="s">
+        <v>626</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>628</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G27" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="20" customHeight="1">
+      <c r="A28" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>627</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G28" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="20" customHeight="1">
+      <c r="A29" s="20" t="s">
+        <v>633</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>569</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="20" customHeight="1">
+      <c r="A30" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G30" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="20" customHeight="1">
+      <c r="A31" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G31" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="20" customHeight="1">
+      <c r="A32" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>574</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G32" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="20" customHeight="1">
+      <c r="A33" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="20" customHeight="1">
+      <c r="A34" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>606</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G34" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20" customHeight="1">
+      <c r="A35" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>564</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>598</v>
+      </c>
+      <c r="G35" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20" customHeight="1">
+      <c r="A36" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20" customHeight="1">
+      <c r="A37" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>584</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20" customHeight="1">
+      <c r="A38" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20" customHeight="1">
+      <c r="A39" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>651</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>652</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:H3"/>
+  <autoFilter ref="A2:H39"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -10849,7 +12223,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -10860,39 +12234,364 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26" customHeight="1">
-      <c r="A1" s="80" t="s">
-        <v>561</v>
-      </c>
-      <c r="B1" s="80" t="s">
-        <v>562</v>
-      </c>
-      <c r="C1" s="80" t="s">
-        <v>563</v>
-      </c>
-      <c r="D1" s="80" t="s">
+      <c r="A1" s="81" t="s">
+        <v>654</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>655</v>
+      </c>
+      <c r="C1" s="81" t="s">
+        <v>656</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>657</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20" customHeight="1">
+      <c r="A2" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>660</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>661</v>
+      </c>
+      <c r="D2" s="84">
+        <v>13</v>
+      </c>
+      <c r="E2" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20" customHeight="1">
+      <c r="A3" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B3" s="82" t="s">
+        <v>663</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>664</v>
+      </c>
+      <c r="D3" s="84">
+        <v>3</v>
+      </c>
+      <c r="E3" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20" customHeight="1">
+      <c r="A4" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B4" s="82" t="s">
+        <v>665</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>666</v>
+      </c>
+      <c r="D4" s="84">
+        <v>2</v>
+      </c>
+      <c r="E4" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20" customHeight="1">
+      <c r="A5" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B5" s="82" t="s">
+        <v>668</v>
+      </c>
+      <c r="C5" s="83" t="s">
+        <v>669</v>
+      </c>
+      <c r="D5" s="84">
+        <v>3</v>
+      </c>
+      <c r="E5" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1">
+      <c r="A6" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B6" s="82" t="s">
+        <v>670</v>
+      </c>
+      <c r="C6" s="83" t="s">
+        <v>671</v>
+      </c>
+      <c r="D6" s="84">
+        <v>3</v>
+      </c>
+      <c r="E6" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20" customHeight="1">
+      <c r="A7" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B7" s="82" t="s">
+        <v>672</v>
+      </c>
+      <c r="C7" s="83" t="s">
+        <v>673</v>
+      </c>
+      <c r="D7" s="84">
+        <v>3</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20" customHeight="1">
+      <c r="A8" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>674</v>
+      </c>
+      <c r="C8" s="83" t="s">
+        <v>675</v>
+      </c>
+      <c r="D8" s="84">
+        <v>16</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20" customHeight="1">
+      <c r="A9" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B9" s="82" t="s">
+        <v>676</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>677</v>
+      </c>
+      <c r="D9" s="84">
+        <v>3</v>
+      </c>
+      <c r="E9" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20" customHeight="1">
+      <c r="A10" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>678</v>
+      </c>
+      <c r="C10" s="83" t="s">
+        <v>679</v>
+      </c>
+      <c r="D10" s="84">
+        <v>18</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1">
+      <c r="A11" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B11" s="82" t="s">
+        <v>680</v>
+      </c>
+      <c r="C11" s="83" t="s">
+        <v>681</v>
+      </c>
+      <c r="D11" s="84">
+        <v>3</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1">
+      <c r="A12" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>603</v>
+      </c>
+      <c r="C12" s="83" t="s">
+        <v>682</v>
+      </c>
+      <c r="D12" s="84">
+        <v>9</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20" customHeight="1">
+      <c r="A13" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B13" s="82" t="s">
+        <v>606</v>
+      </c>
+      <c r="C13" s="83" t="s">
+        <v>683</v>
+      </c>
+      <c r="D13" s="84">
+        <v>4</v>
+      </c>
+      <c r="E13" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="20" customHeight="1">
+      <c r="A14" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B14" s="82" t="s">
         <v>564</v>
       </c>
-      <c r="E1" s="80" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="28" customHeight="1">
-      <c r="A2" s="81" t="s">
-        <v>566</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="81">
-        <v>0</v>
-      </c>
-      <c r="E2" s="81" t="s">
-        <v>567</v>
+      <c r="C14" s="83" t="s">
+        <v>684</v>
+      </c>
+      <c r="D14" s="84">
+        <v>10</v>
+      </c>
+      <c r="E14" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="20" customHeight="1">
+      <c r="A15" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>646</v>
+      </c>
+      <c r="C15" s="83" t="s">
+        <v>685</v>
+      </c>
+      <c r="D15" s="84">
+        <v>3</v>
+      </c>
+      <c r="E15" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1">
+      <c r="A16" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>686</v>
+      </c>
+      <c r="C16" s="83" t="s">
+        <v>687</v>
+      </c>
+      <c r="D16" s="84">
+        <v>1</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="20" customHeight="1">
+      <c r="A17" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>688</v>
+      </c>
+      <c r="C17" s="83" t="s">
+        <v>689</v>
+      </c>
+      <c r="D17" s="84">
+        <v>1</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="20" customHeight="1">
+      <c r="A18" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>690</v>
+      </c>
+      <c r="C18" s="83" t="s">
+        <v>691</v>
+      </c>
+      <c r="D18" s="84">
+        <v>1</v>
+      </c>
+      <c r="E18" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="20" customHeight="1">
+      <c r="A19" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B19" s="82" t="s">
+        <v>634</v>
+      </c>
+      <c r="C19" s="83" t="s">
+        <v>692</v>
+      </c>
+      <c r="D19" s="84">
+        <v>1</v>
+      </c>
+      <c r="E19" s="82" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="20" customHeight="1">
+      <c r="A20" s="82" t="s">
+        <v>659</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>693</v>
+      </c>
+      <c r="C20" s="83" t="s">
+        <v>694</v>
+      </c>
+      <c r="D20" s="84">
+        <v>1</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28" customHeight="1">
+      <c r="A21" s="85" t="s">
+        <v>695</v>
+      </c>
+      <c r="B21" s="85"/>
+      <c r="C21" s="86" t="s">
+        <v>696</v>
+      </c>
+      <c r="D21" s="85">
+        <v>98</v>
+      </c>
+      <c r="E21" s="85" t="s">
+        <v>697</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E20"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10910,7 +12609,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="79" t="s">
-        <v>568</v>
+        <v>698</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -10922,314 +12621,314 @@
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
       <c r="A2" s="79" t="s">
-        <v>569</v>
+        <v>699</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>571</v>
+        <v>701</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>572</v>
+        <v>702</v>
       </c>
       <c r="E2" s="79" t="s">
-        <v>573</v>
+        <v>703</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>574</v>
+        <v>704</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>575</v>
+        <v>705</v>
       </c>
       <c r="H2" s="79" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="182" customHeight="1">
-      <c r="A3" s="83" t="s">
-        <v>576</v>
+      <c r="A3" s="87" t="s">
+        <v>706</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>578</v>
+        <v>707</v>
+      </c>
+      <c r="C3" s="88" t="s">
+        <v>708</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>579</v>
+        <v>709</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>580</v>
+        <v>710</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>581</v>
+        <v>711</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>583</v>
+        <v>713</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1">
-      <c r="A4" s="83" t="s">
-        <v>584</v>
+      <c r="A4" s="87" t="s">
+        <v>714</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>585</v>
-      </c>
-      <c r="C4" s="84" t="s">
-        <v>586</v>
+        <v>715</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>716</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>587</v>
+        <v>717</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>588</v>
+        <v>718</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>589</v>
+        <v>719</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>590</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1">
-      <c r="A5" s="83" t="s">
-        <v>591</v>
+      <c r="A5" s="87" t="s">
+        <v>721</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>592</v>
-      </c>
-      <c r="C5" s="84" t="s">
-        <v>586</v>
+        <v>722</v>
+      </c>
+      <c r="C5" s="88" t="s">
+        <v>716</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>587</v>
+        <v>717</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>593</v>
+        <v>723</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>589</v>
+        <v>719</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>594</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="84" customHeight="1">
-      <c r="A6" s="83" t="s">
-        <v>589</v>
+      <c r="A6" s="87" t="s">
+        <v>719</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>595</v>
-      </c>
-      <c r="C6" s="84" t="s">
-        <v>596</v>
+        <v>725</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>726</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>597</v>
+        <v>727</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>598</v>
+        <v>728</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>599</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1">
-      <c r="A7" s="83" t="s">
-        <v>600</v>
+      <c r="A7" s="87" t="s">
+        <v>730</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>601</v>
-      </c>
-      <c r="C7" s="84" t="s">
-        <v>602</v>
+        <v>731</v>
+      </c>
+      <c r="C7" s="88" t="s">
+        <v>732</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>603</v>
+        <v>733</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>604</v>
+        <v>734</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>605</v>
+        <v>735</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>606</v>
+        <v>736</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>607</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" customHeight="1">
-      <c r="A8" s="83" t="s">
-        <v>608</v>
+      <c r="A8" s="87" t="s">
+        <v>738</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>609</v>
-      </c>
-      <c r="C8" s="84" t="s">
-        <v>610</v>
+        <v>739</v>
+      </c>
+      <c r="C8" s="88" t="s">
+        <v>740</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>611</v>
+        <v>741</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>612</v>
+        <v>742</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>613</v>
+        <v>743</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>614</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" customHeight="1">
-      <c r="A9" s="83" t="s">
-        <v>615</v>
+      <c r="A9" s="87" t="s">
+        <v>745</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="C9" s="84" t="s">
-        <v>617</v>
+        <v>746</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>747</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>618</v>
+        <v>748</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>619</v>
+        <v>749</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>620</v>
+        <v>750</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>621</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1">
-      <c r="A10" s="85" t="s">
-        <v>622</v>
-      </c>
-      <c r="B10" s="86" t="s">
-        <v>623</v>
-      </c>
-      <c r="C10" s="84" t="s">
-        <v>624</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="86" t="s">
-        <v>625</v>
-      </c>
-      <c r="F10" s="86" t="s">
-        <v>626</v>
-      </c>
-      <c r="G10" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="86" t="s">
-        <v>627</v>
+      <c r="A10" s="89" t="s">
+        <v>752</v>
+      </c>
+      <c r="B10" s="90" t="s">
+        <v>753</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>754</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>755</v>
+      </c>
+      <c r="F10" s="90" t="s">
+        <v>756</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="90" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1">
-      <c r="A11" s="85" t="s">
-        <v>628</v>
-      </c>
-      <c r="B11" s="86" t="s">
-        <v>629</v>
-      </c>
-      <c r="C11" s="84" t="s">
-        <v>624</v>
-      </c>
-      <c r="D11" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="86" t="s">
-        <v>630</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>631</v>
-      </c>
-      <c r="G11" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="86" t="s">
-        <v>632</v>
+      <c r="A11" s="89" t="s">
+        <v>758</v>
+      </c>
+      <c r="B11" s="90" t="s">
+        <v>759</v>
+      </c>
+      <c r="C11" s="88" t="s">
+        <v>754</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="90" t="s">
+        <v>760</v>
+      </c>
+      <c r="F11" s="90" t="s">
+        <v>761</v>
+      </c>
+      <c r="G11" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="90" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1">
-      <c r="A12" s="85" t="s">
-        <v>633</v>
-      </c>
-      <c r="B12" s="86" t="s">
-        <v>634</v>
-      </c>
-      <c r="C12" s="84" t="s">
-        <v>635</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="86" t="s">
-        <v>636</v>
-      </c>
-      <c r="F12" s="86" t="s">
-        <v>637</v>
-      </c>
-      <c r="G12" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="86" t="s">
-        <v>638</v>
+      <c r="A12" s="89" t="s">
+        <v>763</v>
+      </c>
+      <c r="B12" s="90" t="s">
+        <v>764</v>
+      </c>
+      <c r="C12" s="88" t="s">
+        <v>765</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="90" t="s">
+        <v>766</v>
+      </c>
+      <c r="F12" s="90" t="s">
+        <v>767</v>
+      </c>
+      <c r="G12" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="90" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1">
-      <c r="A13" s="85" t="s">
-        <v>639</v>
-      </c>
-      <c r="B13" s="86" t="s">
-        <v>640</v>
-      </c>
-      <c r="C13" s="84" t="s">
-        <v>641</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="86" t="s">
-        <v>642</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>643</v>
-      </c>
-      <c r="G13" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="86" t="s">
-        <v>644</v>
+      <c r="A13" s="89" t="s">
+        <v>769</v>
+      </c>
+      <c r="B13" s="90" t="s">
+        <v>770</v>
+      </c>
+      <c r="C13" s="88" t="s">
+        <v>771</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="90" t="s">
+        <v>772</v>
+      </c>
+      <c r="F13" s="90" t="s">
+        <v>773</v>
+      </c>
+      <c r="G13" s="90" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="90" t="s">
+        <v>774</v>
       </c>
     </row>
   </sheetData>
@@ -11255,172 +12954,172 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
-      <c r="A1" s="87" t="s">
-        <v>645</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
+      <c r="A1" s="91" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
-      <c r="A2" s="87" t="s">
-        <v>646</v>
-      </c>
-      <c r="B2" s="87" t="s">
-        <v>647</v>
-      </c>
-      <c r="C2" s="87" t="s">
-        <v>648</v>
+      <c r="A2" s="91" t="s">
+        <v>776</v>
+      </c>
+      <c r="B2" s="91" t="s">
+        <v>777</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1">
-      <c r="A3" s="88" t="s">
-        <v>649</v>
-      </c>
-      <c r="B3" s="89" t="s">
-        <v>650</v>
-      </c>
-      <c r="C3" s="90" t="s">
-        <v>651</v>
+      <c r="A3" s="92" t="s">
+        <v>779</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>780</v>
+      </c>
+      <c r="C3" s="94" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
-      <c r="A4" s="91" t="s">
-        <v>652</v>
-      </c>
-      <c r="B4" s="90" t="s">
-        <v>653</v>
-      </c>
-      <c r="C4" s="90" t="s">
-        <v>654</v>
+      <c r="A4" s="95" t="s">
+        <v>782</v>
+      </c>
+      <c r="B4" s="94" t="s">
+        <v>783</v>
+      </c>
+      <c r="C4" s="94" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1">
-      <c r="A5" s="91" t="s">
-        <v>655</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>656</v>
-      </c>
-      <c r="C5" s="90" t="s">
-        <v>657</v>
+      <c r="A5" s="95" t="s">
+        <v>785</v>
+      </c>
+      <c r="B5" s="94" t="s">
+        <v>786</v>
+      </c>
+      <c r="C5" s="94" t="s">
+        <v>787</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1">
-      <c r="A6" s="91" t="s">
-        <v>658</v>
-      </c>
-      <c r="B6" s="90" t="s">
-        <v>659</v>
-      </c>
-      <c r="C6" s="90" t="s">
-        <v>660</v>
+      <c r="A6" s="95" t="s">
+        <v>788</v>
+      </c>
+      <c r="B6" s="94" t="s">
+        <v>789</v>
+      </c>
+      <c r="C6" s="94" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1">
-      <c r="A7" s="91" t="s">
-        <v>661</v>
-      </c>
-      <c r="B7" s="90" t="s">
-        <v>662</v>
-      </c>
-      <c r="C7" s="90" t="s">
-        <v>663</v>
+      <c r="A7" s="95" t="s">
+        <v>791</v>
+      </c>
+      <c r="B7" s="94" t="s">
+        <v>792</v>
+      </c>
+      <c r="C7" s="94" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20" customHeight="1">
-      <c r="A8" s="91" t="s">
-        <v>664</v>
-      </c>
-      <c r="B8" s="90" t="s">
-        <v>665</v>
-      </c>
-      <c r="C8" s="90" t="s">
-        <v>666</v>
+      <c r="A8" s="95" t="s">
+        <v>794</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>795</v>
+      </c>
+      <c r="C8" s="94" t="s">
+        <v>796</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20" customHeight="1">
-      <c r="A9" s="91" t="s">
-        <v>667</v>
-      </c>
-      <c r="B9" s="90" t="s">
-        <v>668</v>
-      </c>
-      <c r="C9" s="90" t="s">
-        <v>669</v>
+      <c r="A9" s="95" t="s">
+        <v>797</v>
+      </c>
+      <c r="B9" s="94" t="s">
+        <v>798</v>
+      </c>
+      <c r="C9" s="94" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20" customHeight="1">
-      <c r="A10" s="91" t="s">
-        <v>670</v>
-      </c>
-      <c r="B10" s="90" t="s">
-        <v>671</v>
-      </c>
-      <c r="C10" s="90" t="s">
-        <v>672</v>
+      <c r="A10" s="95" t="s">
+        <v>800</v>
+      </c>
+      <c r="B10" s="94" t="s">
+        <v>801</v>
+      </c>
+      <c r="C10" s="94" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20" customHeight="1">
-      <c r="A11" s="92" t="s">
-        <v>673</v>
-      </c>
-      <c r="B11" s="93" t="s">
-        <v>674</v>
-      </c>
-      <c r="C11" s="90" t="s">
-        <v>675</v>
+      <c r="A11" s="96" t="s">
+        <v>803</v>
+      </c>
+      <c r="B11" s="97" t="s">
+        <v>804</v>
+      </c>
+      <c r="C11" s="94" t="s">
+        <v>805</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1">
-      <c r="A12" s="94" t="s">
-        <v>673</v>
-      </c>
-      <c r="B12" s="95" t="s">
-        <v>676</v>
-      </c>
-      <c r="C12" s="90" t="s">
-        <v>677</v>
+      <c r="A12" s="98" t="s">
+        <v>803</v>
+      </c>
+      <c r="B12" s="99" t="s">
+        <v>806</v>
+      </c>
+      <c r="C12" s="94" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20" customHeight="1">
-      <c r="A13" s="96" t="s">
-        <v>678</v>
-      </c>
-      <c r="B13" s="97" t="s">
-        <v>679</v>
-      </c>
-      <c r="C13" s="90" t="s">
-        <v>680</v>
+      <c r="A13" s="100" t="s">
+        <v>808</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>809</v>
+      </c>
+      <c r="C13" s="94" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20" customHeight="1">
-      <c r="A14" s="91" t="s">
-        <v>681</v>
-      </c>
-      <c r="B14" s="90" t="s">
-        <v>682</v>
-      </c>
-      <c r="C14" s="90" t="s">
-        <v>683</v>
+      <c r="A14" s="95" t="s">
+        <v>811</v>
+      </c>
+      <c r="B14" s="94" t="s">
+        <v>812</v>
+      </c>
+      <c r="C14" s="94" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20" customHeight="1">
-      <c r="A15" s="91" t="s">
-        <v>684</v>
-      </c>
-      <c r="B15" s="90" t="s">
-        <v>685</v>
-      </c>
-      <c r="C15" s="98" t="s">
+      <c r="A15" s="95" t="s">
+        <v>814</v>
+      </c>
+      <c r="B15" s="94" t="s">
+        <v>815</v>
+      </c>
+      <c r="C15" s="102" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1">
-      <c r="A16" s="98" t="s">
-        <v>686</v>
-      </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
+      <c r="A16" s="102" t="s">
+        <v>816</v>
+      </c>
+      <c r="B16" s="102"/>
+      <c r="C16" s="102"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Component CI Matrix'!$A$2:$V$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Framework Detail'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$E$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'InferenceMAX Workflows'!$A$2:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Runner Inventory'!$A$7:$K$30</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2808" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="797">
   <si>
     <t>Category</t>
   </si>
@@ -2129,78 +2129,18 @@
     <t>AMD</t>
   </si>
   <si>
-    <t>b200</t>
-  </si>
-  <si>
-    <t>b200-dgxc_1, b200-dgxc_2, b200-nb_0, b200-nb_1, b200-dgxc-slurm_0, b200-dgxc-slurm_1, b200-dgxc-slurm_2, b200-dgxc-slurm_3, b200-dgxc-slurm_4, b200-dgxc-slurm_5, b200-dgxc-slurm_6, b200-dgxc-slurm_7, b200-dgxc-slurm_8</t>
+    <t>mi300x-amd_0, mi300x-amd_1, mi300x-amd_2, mi300x-amd_3, mi300x-amd_4, mi300x-amds_0, mi300x-amds_1, mi300x-amds_2, mi300x-amds_3</t>
   </si>
   <si>
     <t>SLURM</t>
   </si>
   <si>
-    <t>b200-multinode</t>
-  </si>
-  <si>
-    <t>b200-dgxc-slurm_6, b200-dgxc-slurm_7, b200-dgxc-slurm_8</t>
-  </si>
-  <si>
-    <t>b200-trt</t>
-  </si>
-  <si>
-    <t>b200-nb_0, b200-nb_1</t>
+    <t>mi325x-amd_0, mi325x-amd_1, mi325x-amd_2, mi325x-amd_3</t>
   </si>
   <si>
     <t>Docker/Self-hosted</t>
   </si>
   <si>
-    <t>b300</t>
-  </si>
-  <si>
-    <t>b300-nv_0, b300-nv_1, b300-nv_2</t>
-  </si>
-  <si>
-    <t>gb200</t>
-  </si>
-  <si>
-    <t>gb200-nv_0, gb200-nv_1, gb200-nv_2</t>
-  </si>
-  <si>
-    <t>gb300</t>
-  </si>
-  <si>
-    <t>gb300-nv_0, gb300-nv_1, gb300-nv_2</t>
-  </si>
-  <si>
-    <t>h100</t>
-  </si>
-  <si>
-    <t>h100-cr_0, h100-cr_1, h100-cw_0, h100-cw_1, h100-dgxc-slurm_0, h100-dgxc-slurm_1, h100-dgxc-slurm_2, h100-dgxc-slurm_3, h100-dgxc-slurm_4, h100-dgxc-slurm_5, h100-dgxc-slurm_6, h100-dgxc-slurm_7, h100-dgxc-slurm_8, h100-dgxc-slurm_9, h100-dgxc-slurm_10, h100-dgxc-slurm_11</t>
-  </si>
-  <si>
-    <t>h100-multinode</t>
-  </si>
-  <si>
-    <t>h100-dgxc-slurm_9, h100-dgxc-slurm_10, h100-dgxc-slurm_11</t>
-  </si>
-  <si>
-    <t>h200</t>
-  </si>
-  <si>
-    <t>h200-cw_2, h200-cw_3, h200-nb_0, h200-nb_1, h200-dgxc-slurm_0, h200-dgxc-slurm_1, h200-dgxc-slurm_2, h200-dgxc-slurm_3, h200-dgxc-slurm_4, h200-dgxc-slurm_5, h200-dgxc-slurm_6, h200-dgxc-slurm_7, h200-dgxc-slurm_8, h200-dgxc-slurm_9, h200-dgxc-slurm_10, h200-dgxc-slurm_11, h200-dgxc-slurm_12, h200-dgxc-slurm_13</t>
-  </si>
-  <si>
-    <t>h200-multinode</t>
-  </si>
-  <si>
-    <t>h200-dgxc-slurm_11, h200-dgxc-slurm_12, h200-dgxc-slurm_13</t>
-  </si>
-  <si>
-    <t>mi300x-amd_0, mi300x-amd_1, mi300x-amd_2, mi300x-amd_3, mi300x-amd_4, mi300x-amds_0, mi300x-amds_1, mi300x-amds_2, mi300x-amds_3</t>
-  </si>
-  <si>
-    <t>mi325x-amd_0, mi325x-amd_1, mi325x-amd_2, mi325x-amd_3</t>
-  </si>
-  <si>
     <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2, mi355x-amds_3, mi355x-amds_4, mi355x-amds_5, mi355x-amds_6, mi355x-amds_7, mi355x-amds_8, mi355x-amd_p01_g06</t>
   </si>
   <si>
@@ -2237,10 +2177,10 @@
     <t>Total AMD Inference Nodes</t>
   </si>
   <si>
-    <t>b200: 13  •  b200-multinode: 3  •  b200-trt: 2  •  b300: 3  •  gb200: 3  •  gb300: 3  •  h100: 16  •  h100-multinode: 3  •  h200: 18  •  h200-multinode: 3  •  mi300x: 9  •  mi325x: 4  •  mi355x: 10  •  mi355x-disagg: 3  •  mi355x-m15-17: 1  •  mi355x-p02-g09: 1  •  mi355x-p02-g17: 1  •  mi355x-p02-g42: 1  •  mi355x-tw-sctrl: 1</t>
-  </si>
-  <si>
-    <t>19 GPU pool types</t>
+    <t>mi300x: 9  •  mi325x: 4  •  mi355x: 10  •  mi355x-disagg: 3  •  mi355x-m15-17: 1  •  mi355x-p02-g09: 1  •  mi355x-p02-g17: 1  •  mi355x-p02-g42: 1  •  mi355x-tw-sctrl: 1</t>
+  </si>
+  <si>
+    <t>9 GPU pool types</t>
   </si>
   <si>
     <t>InferenceMAX CI Workflows — ROCm/InferenceMAX_rocm (.github/workflows/)</t>
@@ -12223,7 +12163,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -12255,16 +12195,16 @@
         <v>659</v>
       </c>
       <c r="B2" s="82" t="s">
+        <v>603</v>
+      </c>
+      <c r="C2" s="83" t="s">
         <v>660</v>
       </c>
-      <c r="C2" s="83" t="s">
+      <c r="D2" s="84">
+        <v>9</v>
+      </c>
+      <c r="E2" s="82" t="s">
         <v>661</v>
-      </c>
-      <c r="D2" s="84">
-        <v>13</v>
-      </c>
-      <c r="E2" s="82" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20" customHeight="1">
@@ -12272,16 +12212,16 @@
         <v>659</v>
       </c>
       <c r="B3" s="82" t="s">
+        <v>606</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>662</v>
+      </c>
+      <c r="D3" s="84">
+        <v>4</v>
+      </c>
+      <c r="E3" s="82" t="s">
         <v>663</v>
-      </c>
-      <c r="C3" s="83" t="s">
-        <v>664</v>
-      </c>
-      <c r="D3" s="84">
-        <v>3</v>
-      </c>
-      <c r="E3" s="82" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="20" customHeight="1">
@@ -12289,16 +12229,16 @@
         <v>659</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>665</v>
+        <v>564</v>
       </c>
       <c r="C4" s="83" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D4" s="84">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="20" customHeight="1">
@@ -12306,16 +12246,16 @@
         <v>659</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>668</v>
+        <v>646</v>
       </c>
       <c r="C5" s="83" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D5" s="84">
         <v>3</v>
       </c>
       <c r="E5" s="82" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
@@ -12323,16 +12263,16 @@
         <v>659</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C6" s="83" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D6" s="84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" s="82" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20" customHeight="1">
@@ -12340,16 +12280,16 @@
         <v>659</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C7" s="83" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D7" s="84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="82" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20" customHeight="1">
@@ -12357,16 +12297,16 @@
         <v>659</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C8" s="83" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D8" s="84">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="20" customHeight="1">
@@ -12374,16 +12314,16 @@
         <v>659</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>676</v>
+        <v>634</v>
       </c>
       <c r="C9" s="83" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D9" s="84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="82" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="20" customHeight="1">
@@ -12391,207 +12331,37 @@
         <v>659</v>
       </c>
       <c r="B10" s="82" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="C10" s="83" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="D10" s="84">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E10" s="82" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="20" customHeight="1">
-      <c r="A11" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B11" s="82" t="s">
-        <v>680</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>681</v>
-      </c>
-      <c r="D11" s="84">
-        <v>3</v>
-      </c>
-      <c r="E11" s="82" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1">
-      <c r="A12" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B12" s="82" t="s">
-        <v>603</v>
-      </c>
-      <c r="C12" s="83" t="s">
-        <v>682</v>
-      </c>
-      <c r="D12" s="84">
-        <v>9</v>
-      </c>
-      <c r="E12" s="82" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="20" customHeight="1">
-      <c r="A13" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>606</v>
-      </c>
-      <c r="C13" s="83" t="s">
-        <v>683</v>
-      </c>
-      <c r="D13" s="84">
-        <v>4</v>
-      </c>
-      <c r="E13" s="82" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20" customHeight="1">
-      <c r="A14" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B14" s="82" t="s">
-        <v>564</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>684</v>
-      </c>
-      <c r="D14" s="84">
-        <v>10</v>
-      </c>
-      <c r="E14" s="82" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="20" customHeight="1">
-      <c r="A15" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B15" s="82" t="s">
-        <v>646</v>
-      </c>
-      <c r="C15" s="83" t="s">
-        <v>685</v>
-      </c>
-      <c r="D15" s="84">
-        <v>3</v>
-      </c>
-      <c r="E15" s="82" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="A16" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B16" s="82" t="s">
-        <v>686</v>
-      </c>
-      <c r="C16" s="83" t="s">
-        <v>687</v>
-      </c>
-      <c r="D16" s="84">
-        <v>1</v>
-      </c>
-      <c r="E16" s="82" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="20" customHeight="1">
-      <c r="A17" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>688</v>
-      </c>
-      <c r="C17" s="83" t="s">
-        <v>689</v>
-      </c>
-      <c r="D17" s="84">
-        <v>1</v>
-      </c>
-      <c r="E17" s="82" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="20" customHeight="1">
-      <c r="A18" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>690</v>
-      </c>
-      <c r="C18" s="83" t="s">
-        <v>691</v>
-      </c>
-      <c r="D18" s="84">
-        <v>1</v>
-      </c>
-      <c r="E18" s="82" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="20" customHeight="1">
-      <c r="A19" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B19" s="82" t="s">
-        <v>634</v>
-      </c>
-      <c r="C19" s="83" t="s">
-        <v>692</v>
-      </c>
-      <c r="D19" s="84">
-        <v>1</v>
-      </c>
-      <c r="E19" s="82" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="20" customHeight="1">
-      <c r="A20" s="82" t="s">
-        <v>659</v>
-      </c>
-      <c r="B20" s="82" t="s">
-        <v>693</v>
-      </c>
-      <c r="C20" s="83" t="s">
-        <v>694</v>
-      </c>
-      <c r="D20" s="84">
-        <v>1</v>
-      </c>
-      <c r="E20" s="82" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="28" customHeight="1">
-      <c r="A21" s="85" t="s">
-        <v>695</v>
-      </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="86" t="s">
-        <v>696</v>
-      </c>
-      <c r="D21" s="85">
-        <v>98</v>
-      </c>
-      <c r="E21" s="85" t="s">
-        <v>697</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28" customHeight="1">
+      <c r="A11" s="85" t="s">
+        <v>675</v>
+      </c>
+      <c r="B11" s="85"/>
+      <c r="C11" s="86" t="s">
+        <v>676</v>
+      </c>
+      <c r="D11" s="85">
+        <v>31</v>
+      </c>
+      <c r="E11" s="85" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E20"/>
+  <autoFilter ref="A1:E10"/>
   <mergeCells count="1">
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12609,7 +12379,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="79" t="s">
-        <v>698</v>
+        <v>678</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -12621,25 +12391,25 @@
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
       <c r="A2" s="79" t="s">
-        <v>699</v>
+        <v>679</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>701</v>
+        <v>681</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>702</v>
+        <v>682</v>
       </c>
       <c r="E2" s="79" t="s">
-        <v>703</v>
+        <v>683</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>704</v>
+        <v>684</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>705</v>
+        <v>685</v>
       </c>
       <c r="H2" s="79" t="s">
         <v>9</v>
@@ -12647,288 +12417,288 @@
     </row>
     <row r="3" spans="1:8" ht="182" customHeight="1">
       <c r="A3" s="87" t="s">
-        <v>706</v>
+        <v>686</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="C3" s="88" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>713</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1">
       <c r="A4" s="87" t="s">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>715</v>
+        <v>695</v>
       </c>
       <c r="C4" s="88" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>720</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1">
       <c r="A5" s="87" t="s">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="84" customHeight="1">
       <c r="A6" s="87" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>727</v>
+        <v>707</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>712</v>
+        <v>692</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>729</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1">
       <c r="A7" s="87" t="s">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>731</v>
+        <v>711</v>
       </c>
       <c r="C7" s="88" t="s">
-        <v>732</v>
+        <v>712</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>733</v>
+        <v>713</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>734</v>
+        <v>714</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>735</v>
+        <v>715</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>736</v>
+        <v>716</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>737</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" customHeight="1">
       <c r="A8" s="87" t="s">
-        <v>738</v>
+        <v>718</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>739</v>
+        <v>719</v>
       </c>
       <c r="C8" s="88" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>741</v>
+        <v>721</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>742</v>
+        <v>722</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>743</v>
+        <v>723</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>744</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" customHeight="1">
       <c r="A9" s="87" t="s">
-        <v>745</v>
+        <v>725</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>746</v>
+        <v>726</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>747</v>
+        <v>727</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>749</v>
+        <v>729</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="89" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>753</v>
+        <v>733</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="D10" s="90" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="90" t="s">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="F10" s="90" t="s">
-        <v>756</v>
+        <v>736</v>
       </c>
       <c r="G10" s="90" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="90" t="s">
-        <v>757</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1">
       <c r="A11" s="89" t="s">
-        <v>758</v>
+        <v>738</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
       <c r="C11" s="88" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="D11" s="90" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="90" t="s">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="F11" s="90" t="s">
-        <v>761</v>
+        <v>741</v>
       </c>
       <c r="G11" s="90" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="90" t="s">
-        <v>762</v>
+        <v>742</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1">
       <c r="A12" s="89" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="B12" s="90" t="s">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="D12" s="90" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="90" t="s">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="F12" s="90" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="G12" s="90" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="90" t="s">
-        <v>768</v>
+        <v>748</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1">
       <c r="A13" s="89" t="s">
-        <v>769</v>
+        <v>749</v>
       </c>
       <c r="B13" s="90" t="s">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="D13" s="90" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="90" t="s">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="F13" s="90" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="G13" s="90" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="90" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -12955,160 +12725,160 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
       <c r="A1" s="91" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="B1" s="91"/>
       <c r="C1" s="91"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
       <c r="A2" s="91" t="s">
-        <v>776</v>
+        <v>756</v>
       </c>
       <c r="B2" s="91" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>778</v>
+        <v>758</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1">
       <c r="A3" s="92" t="s">
-        <v>779</v>
+        <v>759</v>
       </c>
       <c r="B3" s="93" t="s">
-        <v>780</v>
+        <v>760</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>781</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
       <c r="A4" s="95" t="s">
-        <v>782</v>
+        <v>762</v>
       </c>
       <c r="B4" s="94" t="s">
-        <v>783</v>
+        <v>763</v>
       </c>
       <c r="C4" s="94" t="s">
-        <v>784</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1">
       <c r="A5" s="95" t="s">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>786</v>
+        <v>766</v>
       </c>
       <c r="C5" s="94" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1">
       <c r="A6" s="95" t="s">
-        <v>788</v>
+        <v>768</v>
       </c>
       <c r="B6" s="94" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="C6" s="94" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1">
       <c r="A7" s="95" t="s">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="B7" s="94" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="C7" s="94" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20" customHeight="1">
       <c r="A8" s="95" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="B8" s="94" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20" customHeight="1">
       <c r="A9" s="95" t="s">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>798</v>
+        <v>778</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20" customHeight="1">
       <c r="A10" s="95" t="s">
-        <v>800</v>
+        <v>780</v>
       </c>
       <c r="B10" s="94" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="C10" s="94" t="s">
-        <v>802</v>
+        <v>782</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20" customHeight="1">
       <c r="A11" s="96" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="B11" s="97" t="s">
-        <v>804</v>
+        <v>784</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>805</v>
+        <v>785</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1">
       <c r="A12" s="98" t="s">
-        <v>803</v>
+        <v>783</v>
       </c>
       <c r="B12" s="99" t="s">
-        <v>806</v>
+        <v>786</v>
       </c>
       <c r="C12" s="94" t="s">
-        <v>807</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20" customHeight="1">
       <c r="A13" s="100" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="B13" s="101" t="s">
-        <v>809</v>
+        <v>789</v>
       </c>
       <c r="C13" s="94" t="s">
-        <v>810</v>
+        <v>790</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20" customHeight="1">
       <c r="A14" s="95" t="s">
-        <v>811</v>
+        <v>791</v>
       </c>
       <c r="B14" s="94" t="s">
-        <v>812</v>
+        <v>792</v>
       </c>
       <c r="C14" s="94" t="s">
-        <v>813</v>
+        <v>793</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20" customHeight="1">
       <c r="A15" s="95" t="s">
-        <v>814</v>
+        <v>794</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>815</v>
+        <v>795</v>
       </c>
       <c r="C15" s="102" t="s">
         <v>22</v>
@@ -13116,7 +12886,7 @@
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1">
       <c r="A16" s="102" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="B16" s="102"/>
       <c r="C16" s="102"/>

--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2830" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2833" uniqueCount="814">
   <si>
     <t>Category</t>
   </si>
@@ -2519,7 +2519,7 @@
     <t>Downloads evaluation artifacts (accuracy/quality metrics) produced during benchmark runs and consolidates them.</t>
   </si>
   <si>
-    <t>How Data Is Fetched — fetch_rocm_data.py pulls from 4 GitHub repos (auth: 5 000 req/hr with GITHUB_TOKEN; unauth: 60 req/hr with local-clone fallback)</t>
+    <t>How Data Is Fetched — fetch_rocm_data.py pulls from 4 GitHub repos via anonymous sparse git clone (public repos) + SSH sparse clone (InferenceMAX_rocm); falls back to committed JSON snapshots if any clone fails</t>
   </si>
   <si>
     <t>File / Endpoint</t>
@@ -2531,13 +2531,13 @@
     <t>GitHub Link</t>
   </si>
   <si>
-    <t>amdgpu_family_matrix.py</t>
+    <t>build_tools/github_actions/amdgpu_family_matrix.py</t>
   </si>
   <si>
     <t>Runner labels per GPU family, GPU ISA strings (gfx94X, gfx950, …), nightly-only flags</t>
   </si>
   <si>
-    <t>https://github.com/ROCm/TheRock/blob/main/amdgpu_family_matrix.py</t>
+    <t>https://github.com/ROCm/TheRock/blob/main/build_tools/github_actions/amdgpu_family_matrix.py</t>
   </si>
   <si>
     <t>BUILD_TOPOLOGY.toml</t>
@@ -2576,24 +2576,33 @@
     <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci.yml</t>
   </si>
   <si>
-    <t>ci_postsubmit.yml</t>
-  </si>
-  <si>
-    <t>Post-commit tier — triggered by submodule bump merges</t>
-  </si>
-  <si>
-    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci_postsubmit.yml</t>
-  </si>
-  <si>
     <t>ci_asan.yml</t>
   </si>
   <si>
-    <t>ASAN sanitizer builds</t>
+    <t>ASAN sanitizer builds (gfx94X test pool)</t>
   </si>
   <si>
     <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci_asan.yml</t>
   </si>
   <si>
+    <t>ci_tsan.yml</t>
+  </si>
+  <si>
+    <t>TSAN sanitizer builds</t>
+  </si>
+  <si>
+    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci_tsan.yml</t>
+  </si>
+  <si>
+    <t>multi_arch_ci.yml</t>
+  </si>
+  <si>
+    <t>Multi-arch CI matrix (Linux + Windows GPU families)</t>
+  </si>
+  <si>
+    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/multi_arch_ci.yml</t>
+  </si>
+  <si>
     <t>multi_arch_release.yml</t>
   </si>
   <si>
@@ -2609,13 +2618,13 @@
     <t>Discovers all library component names (rocBLAS, hipBLAS, MIOpen, rocFFT, …). Every subdirectory is treated as an active CI component.</t>
   </si>
   <si>
-    <t>https://api.github.com/repos/ROCm/rocm-libraries/contents/projects</t>
+    <t>https://github.com/ROCm/rocm-libraries/tree/main/projects</t>
   </si>
   <si>
     <t>Discovers all system component names (RCCL, rocminfo, ROCm-SMI, …).</t>
   </si>
   <si>
-    <t>https://api.github.com/repos/ROCm/rocm-systems/contents/projects</t>
+    <t>https://github.com/ROCm/rocm-systems/tree/main/projects</t>
   </si>
   <si>
     <t>amd-master.yaml</t>
@@ -12992,7 +13001,7 @@
   <sheetPr>
     <tabColor rgb="FF78909C"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -13107,10 +13116,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="20" customHeight="1">
-      <c r="A11" s="97" t="s">
+      <c r="A11" s="96" t="s">
         <v>797</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="95" t="s">
         <v>798</v>
       </c>
       <c r="C11" s="95" t="s">
@@ -13118,21 +13127,21 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1">
-      <c r="A12" s="99" t="s">
-        <v>797</v>
-      </c>
-      <c r="B12" s="100" t="s">
+      <c r="A12" s="97" t="s">
         <v>800</v>
       </c>
+      <c r="B12" s="98" t="s">
+        <v>801</v>
+      </c>
       <c r="C12" s="95" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20" customHeight="1">
-      <c r="A13" s="101" t="s">
-        <v>802</v>
-      </c>
-      <c r="B13" s="102" t="s">
+      <c r="A13" s="99" t="s">
+        <v>800</v>
+      </c>
+      <c r="B13" s="100" t="s">
         <v>803</v>
       </c>
       <c r="C13" s="95" t="s">
@@ -13140,10 +13149,10 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="20" customHeight="1">
-      <c r="A14" s="96" t="s">
+      <c r="A14" s="101" t="s">
         <v>805</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="102" t="s">
         <v>806</v>
       </c>
       <c r="C14" s="95" t="s">
@@ -13157,21 +13166,32 @@
       <c r="B15" s="95" t="s">
         <v>809</v>
       </c>
-      <c r="C15" s="103" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="30" customHeight="1">
-      <c r="A16" s="103" t="s">
+      <c r="C15" s="95" t="s">
         <v>810</v>
       </c>
-      <c r="B16" s="103"/>
-      <c r="C16" s="103"/>
+    </row>
+    <row r="16" spans="1:3" ht="20" customHeight="1">
+      <c r="A16" s="96" t="s">
+        <v>811</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>812</v>
+      </c>
+      <c r="C16" s="103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" customHeight="1">
+      <c r="A17" s="103" t="s">
+        <v>813</v>
+      </c>
+      <c r="B17" s="103"/>
+      <c r="C17" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1"/>
@@ -13186,6 +13206,7 @@
     <hyperlink ref="C12" r:id="rId10"/>
     <hyperlink ref="C13" r:id="rId11"/>
     <hyperlink ref="C14" r:id="rId12"/>
+    <hyperlink ref="C15" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -20,9 +20,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Component CI Matrix'!$A$2:$V$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Framework Detail'!$A$1:$M$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Inference Runners'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'InferenceMAX Workflows'!$A$2:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'InferenceMAX — AMD Benchmarks'!$A$2:$H$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Runner Inventory'!$A$7:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wheel Artifact Publishing'!$A$1:$K$10</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2833" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="836">
   <si>
     <t>Category</t>
   </si>
@@ -1909,231 +1909,285 @@
     <t>Pinned Docker Image</t>
   </si>
   <si>
+    <t>dsr1-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>amd/DeepSeek-R1-0528-MXFP4-Preview</t>
+  </si>
+  <si>
+    <t>dsr1</t>
+  </si>
+  <si>
+    <t>mi355x</t>
+  </si>
+  <si>
+    <t>fp4</t>
+  </si>
+  <si>
+    <t>sglang</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.12-rocm700-mi35x</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>amd/DeepSeek-R1-0528-MXFP4</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>atom</t>
+  </si>
+  <si>
+    <t>rocm/atom:rocm7.2.3_ubuntu24.04_py3.12_pytorch_release_2.10.0_atom20260511</t>
+  </si>
+  <si>
+    <t>dsr1-fp4-mi355x-atom-mtp</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi300x-sglang</t>
+  </si>
+  <si>
+    <t>deepseek-ai/DeepSeek-R1-0528</t>
+  </si>
+  <si>
+    <t>mi300x</t>
+  </si>
+  <si>
+    <t>fp8</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.12-rocm700-mi30x</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>mi325x</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi355x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen3.5-397B-A17B</t>
+  </si>
+  <si>
+    <t>qwen3.5</t>
+  </si>
+  <si>
+    <t>bf16</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang-rocm:v0.5.12-rocm720-mi35x-20260517</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi355x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi300x-sglang</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.12-rocm720-mi30x</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>Qwen/Qwen3.5-397B-A17B-FP8</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-sglang-agentic</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang-rocm:v0.5.10rc0-rocm720-mi35x-20260414</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-atom</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi355x-atom-mtp</t>
+  </si>
+  <si>
+    <t>rocm/atom:rocm7.2.2_ubuntu24.04_py3.12_pytorch_release_2.10.0_atom0.1.2.post</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>amd/Qwen3.5-397B-A17B-MXFP4</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang:v0.5.12-rocm720-mi35x</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp4-mi355x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi300x-sglang</t>
+  </si>
+  <si>
+    <t>glm5-fp8-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>zai-org/GLM-5-FP8</t>
+  </si>
+  <si>
+    <t>glm5</t>
+  </si>
+  <si>
+    <t>glm5-fp8-mi355x-sglang-mtp</t>
+  </si>
+  <si>
     <t>glm5-fp8-mi355x-atom</t>
   </si>
   <si>
-    <t>zai-org/GLM-5-FP8</t>
-  </si>
-  <si>
-    <t>glm5</t>
-  </si>
-  <si>
-    <t>mi355x</t>
-  </si>
-  <si>
-    <t>fp8</t>
-  </si>
-  <si>
-    <t>atom</t>
-  </si>
-  <si>
-    <t>rocm/atom-dev:nightly_202603291522</t>
+    <t>glm5.1-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>amd/GLM-5.1-MXFP4</t>
+  </si>
+  <si>
+    <t>glm5.1</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang-rocm:v0.5.10rc0-rocm720-mi35x-20260415</t>
+  </si>
+  <si>
+    <t>glm5.1-fp4-mi355x-sglang-agentic</t>
+  </si>
+  <si>
+    <t>glm5.1-fp4-mi355x-sglang-agentic_internal</t>
+  </si>
+  <si>
+    <t>glm5.1-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>kimik2.5-int4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>moonshotai/Kimi-K2.5</t>
+  </si>
+  <si>
+    <t>kimik2.5</t>
+  </si>
+  <si>
+    <t>int4</t>
+  </si>
+  <si>
+    <t>vllm</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:v0.21.0</t>
+  </si>
+  <si>
+    <t>kimik2.5-int4-mi325x-vllm</t>
+  </si>
+  <si>
+    <t>kimik2.5-int4-mi300x-vllm</t>
+  </si>
+  <si>
+    <t>kimik2.5-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>amd/Kimi-K2.5-MXFP4</t>
+  </si>
+  <si>
+    <t>kimik2.5-fp4-mi355x-vllm-agentic</t>
   </si>
   <si>
     <t>kimik2.5-fp4-mi355x-atom</t>
   </si>
   <si>
-    <t>amd/Kimi-K2.5-MXFP4</t>
-  </si>
-  <si>
-    <t>kimik2.5</t>
-  </si>
-  <si>
-    <t>fp4</t>
-  </si>
-  <si>
-    <t>rocm/atom-dev:nightly_202603251629</t>
+    <t>minimaxm2.5-fp8-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>MiniMaxAI/MiniMax-M2.5</t>
+  </si>
+  <si>
+    <t>minimaxm2.5</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi355x-vllm-agentic</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:nightly-51f22dcfd068fe8f1e3192da2a1e825b930223cf</t>
   </si>
   <si>
     <t>minimaxm2.5-fp8-mi355x-atom</t>
   </si>
   <si>
-    <t>MiniMaxAI/MiniMax-M2.5</t>
-  </si>
-  <si>
-    <t>minimaxm2.5</t>
+    <t>minimaxm2.5-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>amd/MiniMax-M2.5-MXFP4</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi300x-vllm</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi300x-vllm-agentic</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi325x-vllm</t>
+  </si>
+  <si>
+    <t>minimaxm2.5-fp8-mi325x-vllm-agentic</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi300x-vllm</t>
+  </si>
+  <si>
+    <t>openai/gpt-oss-120b</t>
+  </si>
+  <si>
+    <t>gptoss</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:v0.17.0</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi325x-vllm</t>
+  </si>
+  <si>
+    <t>gptoss-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>amd/gpt-oss-120b-w-mxfp4-a-fp8</t>
   </si>
   <si>
     <t>gptoss-fp4-mi355x-atom</t>
   </si>
   <si>
-    <t>openai/gpt-oss-120b</t>
-  </si>
-  <si>
-    <t>gptoss</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-atom-mtp</t>
-  </si>
-  <si>
-    <t>amd/DeepSeek-R1-0528-MXFP4-MTP-MoEFP4</t>
-  </si>
-  <si>
-    <t>dsr1</t>
-  </si>
-  <si>
-    <t>rocm/atom:rocm7.2.1-ubuntu24.04-pytorch2.9.1-atom0.1.2</t>
+    <t>dsr1-fp8-mi355x-atom</t>
   </si>
   <si>
     <t>dsr1-fp8-mi355x-atom-mtp</t>
   </si>
   <si>
-    <t>deepseek-ai/DeepSeek-R1-0528</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-atom</t>
-  </si>
-  <si>
-    <t>amd/DeepSeek-R1-0528-MXFP4-Preview</t>
-  </si>
-  <si>
-    <t>rocm/atom:rocm7.1.1-ubuntu24.04-pytorch2.9-atom0.1.1-MI350x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-atom</t>
-  </si>
-  <si>
-    <t>dsr1-fp4-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>sglang</t>
-  </si>
-  <si>
-    <t>lmsysorg/sglang:v0.5.9-rocm700-mi35x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi300x-sglang</t>
-  </si>
-  <si>
-    <t>mi300x</t>
-  </si>
-  <si>
-    <t>lmsysorg/sglang:v0.5.9-rocm700-mi30x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi325x-sglang</t>
-  </si>
-  <si>
-    <t>mi325x</t>
-  </si>
-  <si>
-    <t>dsr1-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen3.5-397B-A17B</t>
-  </si>
-  <si>
-    <t>qwen3.5</t>
-  </si>
-  <si>
-    <t>bf16</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260215</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi355x-atom</t>
-  </si>
-  <si>
-    <t>rocm/atom:rocm7.2.1-ubuntu24.04-pytorch2.9.1-atom0.1.2-vllm0.17.0</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi300x-sglang</t>
-  </si>
-  <si>
-    <t>lmsysorg/sglang:v0.5.9-rocm720-mi30x</t>
-  </si>
-  <si>
-    <t>qwen3.5-bf16-mi325x-sglang</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi325x-sglang</t>
-  </si>
-  <si>
-    <t>Qwen/Qwen3.5-397B-A17B-FP8</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260218</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi355x-atom</t>
-  </si>
-  <si>
-    <t>qwen3.5-fp8-mi300x-sglang</t>
-  </si>
-  <si>
-    <t>glm5-fp8-mi355x-sglang</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:v0.5.8.post1-rocm720-mi35x-20260219</t>
-  </si>
-  <si>
-    <t>kimik2.5-int4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>moonshotai/Kimi-K2.5</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g57</t>
-  </si>
-  <si>
-    <t>int4</t>
-  </si>
-  <si>
-    <t>vllm</t>
-  </si>
-  <si>
-    <t>aigmkt/kimi-k25-dev</t>
-  </si>
-  <si>
-    <t>kimik2.5-int4-mi325x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.18.0</t>
-  </si>
-  <si>
-    <t>kimik2.5-fp4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g42</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.15.1</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi300x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.16.0</t>
-  </si>
-  <si>
-    <t>minimaxm2.5-fp8-mi325x-vllm</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi300x-vllm</t>
-  </si>
-  <si>
-    <t>vllm/vllm-openai-rocm:v0.17.0</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi325x-vllm</t>
-  </si>
-  <si>
-    <t>gptoss-fp4-mi355x-vllm</t>
-  </si>
-  <si>
-    <t>amd/gpt-oss-120b-w-mxfp4-a-fp8</t>
-  </si>
-  <si>
     <t>dsr1-fp8-mi355x-sglang-disagg</t>
   </si>
   <si>
@@ -2152,15 +2206,54 @@
     <t>dsr1-fp4-mi355x-sglang-disagg</t>
   </si>
   <si>
-    <t>amd/DeepSeek-R1-0528-MXFP4</t>
-  </si>
-  <si>
-    <t>rocm/sgl-dev:sglang-0.5.9-rocm720-mi35x-mori-0227-3</t>
+    <t>amd/DeepSeek-R1-0528-MXFP4-v2</t>
+  </si>
+  <si>
+    <t>lmsysorg/sglang-rocm:v0.5.10.post1-rocm720-mi35x-20260501</t>
   </si>
   <si>
     <t>dsr1-fp4-mi355x-sglang-disagg-mtp</t>
   </si>
   <si>
+    <t>dsv4-fp4-mi355x-sglang</t>
+  </si>
+  <si>
+    <t>deepseek-ai/DeepSeek-V4-Pro</t>
+  </si>
+  <si>
+    <t>dsv4</t>
+  </si>
+  <si>
+    <t>rocm/sgl-dev:rocm720-mi35x-8c3b5aa-20260521-DSv4</t>
+  </si>
+  <si>
+    <t>dsv4-fp4-mi355x-vllm</t>
+  </si>
+  <si>
+    <t>vllm/vllm-openai-rocm:nightly-4f940896a32c9e2a0eba7f50d521bf5f6b4de458</t>
+  </si>
+  <si>
+    <t>dsv4-fp4-mi355x-atom</t>
+  </si>
+  <si>
+    <t>rocm/atom-dev:nightly_202605130853</t>
+  </si>
+  <si>
+    <t>qwen3.5-bf16-mi325x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>dsr1-fp8-mi325x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>qwen3.5-fp8-mi325x-sglang-mtp</t>
+  </si>
+  <si>
+    <t>glm5-fp8-mi325x-sglang</t>
+  </si>
+  <si>
+    <t>glm5-fp8-mi325x-sglang-mtp</t>
+  </si>
+  <si>
     <t>Ecosystem</t>
   </si>
   <si>
@@ -2179,76 +2272,49 @@
     <t>AMD</t>
   </si>
   <si>
-    <t>mi300x-amd_0, mi300x-amd_1, mi300x-amd_2, mi300x-amd_3, mi300x-amd_4, mi300x-amds_0, mi300x-amds_1, mi300x-amds_2, mi300x-amds_3</t>
+    <t>mi300x-amds_00, mi300x-amds_01, mi300x-amds_02, mi300x-amds_03, mi300x-amds_04, mi300x-amds_05, mi300x-amds_06, mi300x-amds_07, mi300x-amds_08</t>
   </si>
   <si>
     <t>SLURM</t>
   </si>
   <si>
-    <t>Live online/offline NOT tracked by therock-runner-health.com — managed by AMD-S Slurm scheduler | Sub-pools: 4 AMD-S Slurm (amds_*) · 5 Docker/self-hosted (amd_*)</t>
-  </si>
-  <si>
-    <t>mi325x-amd_0, mi325x-amd_1, mi325x-amd_2, mi325x-amd_3</t>
-  </si>
-  <si>
-    <t>Docker/Self-hosted</t>
-  </si>
-  <si>
-    <t>Live online/offline NOT tracked by therock-runner-health.com — self-hosted Docker pool managed by InferenceMAX_rocm | Sub-pools: 4 Docker/self-hosted (amd_*)</t>
-  </si>
-  <si>
-    <t>mi355x-amd_p02g32, mi355x-amd_p02g42, mi355x-amd_p02g57, mi355x-amd_p02g44, mi355x-amd_p01g06, mi355x-amd_p01g07</t>
-  </si>
-  <si>
-    <t>Live online/offline NOT tracked by therock-runner-health.com — self-hosted Docker pool managed by InferenceMAX_rocm | Sub-pools: 6 Docker/self-hosted (amd_*)</t>
-  </si>
-  <si>
-    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2</t>
+    <t>Live online/offline NOT tracked by therock-runner-health.com — managed by AMD-S Slurm scheduler | Sub-pools: 9 AMD-S Slurm (amds_*)</t>
+  </si>
+  <si>
+    <t>mi300x-disagg</t>
+  </si>
+  <si>
+    <t>mi300x-amds_06, mi300x-amds_07, mi300x-amds_08</t>
   </si>
   <si>
     <t>Live online/offline NOT tracked by therock-runner-health.com — managed by AMD-S Slurm scheduler | Sub-pools: 3 AMD-S Slurm (amds_*) | Quirks: disaggregated serving</t>
   </si>
   <si>
-    <t>mi355x-m15-17</t>
-  </si>
-  <si>
-    <t>mi355x-amd</t>
-  </si>
-  <si>
-    <t>Live online/offline NOT tracked by therock-runner-health.com — self-hosted Docker pool managed by InferenceMAX_rocm | Sub-pools: 1 Docker/self-hosted (amd_*)</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g09</t>
-  </si>
-  <si>
-    <t>mi355x-amd_9</t>
-  </si>
-  <si>
-    <t>mi355x-p02-g17</t>
-  </si>
-  <si>
-    <t>mi355x-amd_17</t>
-  </si>
-  <si>
-    <t>mi355x-amd_42</t>
-  </si>
-  <si>
-    <t>mi355x-tw-sctrl</t>
-  </si>
-  <si>
-    <t>mi355x-amds</t>
-  </si>
-  <si>
-    <t>Live online/offline NOT tracked by therock-runner-health.com — managed by AMD-S Slurm scheduler | Sub-pools: 1 AMD-S Slurm (amds_*) | Quirks: spec-decoding / single-controller pool</t>
+    <t>mi325x-amds_00, mi325x-amds_01, mi325x-amds_02, mi325x-amds_03, mi325x-amds_04, mi325x-amds_05, mi325x-amds_06, mi325x-amds_07, mi325x-amds_08</t>
+  </si>
+  <si>
+    <t>mi325x-disagg</t>
+  </si>
+  <si>
+    <t>mi325x-amds_00, mi325x-amds_01, mi325x-amds_02, mi325x-amds_03, mi325x-amds_06, mi325x-amds_07, mi325x-amds_08</t>
+  </si>
+  <si>
+    <t>Live online/offline NOT tracked by therock-runner-health.com — managed by AMD-S Slurm scheduler | Sub-pools: 7 AMD-S Slurm (amds_*) | Quirks: disaggregated serving</t>
+  </si>
+  <si>
+    <t>mi355x-amds_0, mi355x-amds_1, mi355x-amds_2, mi355x-amds_3, mi355x-amds_4, mi355x-amds_5, mi355x-amds_6, mi355x-amds_7, mi355x-amds_8</t>
+  </si>
+  <si>
+    <t>mi355x-amds_6, mi355x-amds_7, mi355x-amds_8</t>
   </si>
   <si>
     <t>Total AMD Inference Nodes</t>
   </si>
   <si>
-    <t>mi300x: 9  •  mi325x: 4  •  mi355x: 6  •  mi355x-disagg: 3  •  mi355x-m15-17: 1  •  mi355x-p02-g09: 1  •  mi355x-p02-g17: 1  •  mi355x-p02-g42: 1  •  mi355x-tw-sctrl: 1</t>
-  </si>
-  <si>
-    <t>9 GPU pool types</t>
+    <t>mi300x: 9  •  mi300x-disagg: 3  •  mi325x: 9  •  mi325x-disagg: 7  •  mi355x: 9  •  mi355x-disagg: 3</t>
+  </si>
+  <si>
+    <t>6 GPU pool types</t>
   </si>
   <si>
     <t>InferenceMAX runners NOT tracked by therock-runner-health.com (separate Slurm + Docker pools managed in ROCm/InferenceMAX_rocm)</t>
@@ -3091,13 +3157,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1565C022"/>
+        <fgColor rgb="FFD4E3F3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1565C011"/>
+        <fgColor rgb="FFE7EFF8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3109,37 +3175,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E7D3222"/>
+        <fgColor rgb="FFD9E7DA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2E7D3211"/>
+        <fgColor rgb="FFEAF2EA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6510022"/>
+        <fgColor rgb="FFFADFD1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6510011"/>
+        <fgColor rgb="FFFCEDE5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A148C22"/>
+        <fgColor rgb="FFDED4EA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A148C11"/>
+        <fgColor rgb="FFECE7F3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11469,13 +11535,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="43.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
@@ -11554,13 +11620,13 @@
         <v>585</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F4" s="20" t="s">
         <v>582</v>
@@ -11569,18 +11635,18 @@
         <v>68</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>580</v>
@@ -11589,7 +11655,7 @@
         <v>581</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="G5" s="80" t="s">
         <v>68</v>
@@ -11600,22 +11666,22 @@
     </row>
     <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E6" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>587</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>582</v>
       </c>
       <c r="G6" s="80" t="s">
         <v>68</v>
@@ -11626,19 +11692,19 @@
     </row>
     <row r="7" spans="1:8" ht="20" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F7" s="20" t="s">
         <v>582</v>
@@ -11647,24 +11713,24 @@
         <v>68</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F8" s="20" t="s">
         <v>582</v>
@@ -11673,24 +11739,24 @@
         <v>68</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>582</v>
@@ -11699,24 +11765,24 @@
         <v>68</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>582</v>
@@ -11725,154 +11791,154 @@
         <v>68</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G11" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B12" s="20" t="s">
         <v>600</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G12" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B13" s="20" t="s">
         <v>600</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G13" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="B14" s="20" t="s">
         <v>600</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G14" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="20" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G15" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>582</v>
@@ -11881,122 +11947,122 @@
         <v>68</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="20" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G17" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="20" customHeight="1">
       <c r="A18" s="20" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G18" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="20" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="G19" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>622</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="20" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="G20" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="20" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>580</v>
@@ -12011,44 +12077,44 @@
         <v>68</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="20" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>581</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="G22" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="20" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>578</v>
+        <v>618</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>580</v>
@@ -12057,355 +12123,1083 @@
         <v>581</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="G23" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="20" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>634</v>
+        <v>592</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>635</v>
+        <v>593</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="G24" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>637</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="20" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>635</v>
+        <v>593</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="G25" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>639</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="20" customHeight="1">
       <c r="A26" s="20" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>585</v>
+        <v>624</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>641</v>
+        <v>580</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="G26" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>639</v>
+        <v>603</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="20" customHeight="1">
       <c r="A27" s="20" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>590</v>
+        <v>624</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>591</v>
+        <v>625</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>636</v>
+        <v>587</v>
       </c>
       <c r="G27" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="20" customHeight="1">
       <c r="A28" s="20" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>590</v>
+        <v>629</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>591</v>
+        <v>630</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="E28" s="20" t="s">
         <v>581</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="G28" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="20" customHeight="1">
       <c r="A29" s="20" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>590</v>
+        <v>629</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>591</v>
+        <v>630</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="E29" s="20" t="s">
         <v>581</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="G29" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="20" customHeight="1">
       <c r="A30" s="20" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>593</v>
+        <v>629</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>594</v>
+        <v>630</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>609</v>
+        <v>580</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="G30" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>648</v>
+        <v>603</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="20" customHeight="1">
       <c r="A31" s="20" t="s">
-        <v>649</v>
+        <v>634</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>593</v>
+        <v>629</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>594</v>
+        <v>630</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>612</v>
+        <v>580</v>
       </c>
       <c r="E31" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F31" s="20" t="s">
         <v>587</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>636</v>
       </c>
       <c r="G31" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>648</v>
+        <v>616</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="20" customHeight="1">
       <c r="A32" s="20" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>651</v>
+        <v>636</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>594</v>
+        <v>637</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>580</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>587</v>
+        <v>638</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="G32" s="80" t="s">
         <v>68</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="20" customHeight="1">
       <c r="A33" s="20" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>600</v>
+        <v>636</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>597</v>
+        <v>637</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>653</v>
+        <v>596</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>581</v>
+        <v>638</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>19</v>
+        <v>639</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>68</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="20" customHeight="1">
       <c r="A34" s="20" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>600</v>
+        <v>636</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>597</v>
+        <v>637</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>653</v>
+        <v>592</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>581</v>
+        <v>638</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>19</v>
+        <v>639</v>
+      </c>
+      <c r="G34" s="80" t="s">
+        <v>68</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>655</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="20" customHeight="1">
       <c r="A35" s="20" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>597</v>
+        <v>637</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>653</v>
+        <v>580</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>19</v>
+        <v>639</v>
+      </c>
+      <c r="G35" s="80" t="s">
+        <v>68</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>659</v>
+        <v>640</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="20" customHeight="1">
       <c r="A36" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G36" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="20" customHeight="1">
+      <c r="A37" s="20" t="s">
+        <v>646</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="G37" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="20" customHeight="1">
+      <c r="A38" s="20" t="s">
+        <v>647</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G38" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="20" customHeight="1">
+      <c r="A39" s="20" t="s">
+        <v>650</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G39" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="20" customHeight="1">
+      <c r="A40" s="20" t="s">
+        <v>652</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="G40" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="20" customHeight="1">
+      <c r="A41" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="G41" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="20" customHeight="1">
+      <c r="A42" s="20" t="s">
+        <v>655</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G42" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="20" customHeight="1">
+      <c r="A43" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G43" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="20" customHeight="1">
+      <c r="A44" s="20" t="s">
+        <v>657</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G44" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="20" customHeight="1">
+      <c r="A45" s="20" t="s">
+        <v>658</v>
+      </c>
+      <c r="B45" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G45" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="20" customHeight="1">
+      <c r="A46" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>648</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>649</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G46" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="20" customHeight="1">
+      <c r="A47" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>658</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>597</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>653</v>
-      </c>
-      <c r="E36" s="20" t="s">
+      <c r="B47" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G47" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="20" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="20" customHeight="1">
+      <c r="A48" s="20" t="s">
+        <v>664</v>
+      </c>
+      <c r="B48" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G48" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="20" customHeight="1">
+      <c r="A49" s="20" t="s">
+        <v>665</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>666</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G49" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H49" s="20" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="20" customHeight="1">
+      <c r="A50" s="20" t="s">
+        <v>667</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>661</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>662</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F50" s="20" t="s">
         <v>587</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>654</v>
-      </c>
-      <c r="G36" s="10" t="s">
+      <c r="G50" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="20" customHeight="1">
+      <c r="A51" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="G51" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="20" customHeight="1">
+      <c r="A52" s="20" t="s">
+        <v>669</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="G52" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" s="20" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="20" customHeight="1">
+      <c r="A53" s="20" t="s">
+        <v>670</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H36" s="20" t="s">
-        <v>659</v>
+      <c r="H53" s="20" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="20" customHeight="1">
+      <c r="A54" s="20" t="s">
+        <v>674</v>
+      </c>
+      <c r="B54" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="20" customHeight="1">
+      <c r="A55" s="20" t="s">
+        <v>675</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" s="20" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="20" customHeight="1">
+      <c r="A56" s="20" t="s">
+        <v>678</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>676</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>671</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>672</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="20" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="20" customHeight="1">
+      <c r="A57" s="20" t="s">
+        <v>679</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D57" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G57" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="20" customHeight="1">
+      <c r="A58" s="20" t="s">
+        <v>683</v>
+      </c>
+      <c r="B58" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>639</v>
+      </c>
+      <c r="G58" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="20" customHeight="1">
+      <c r="A59" s="20" t="s">
+        <v>685</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>680</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>681</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>587</v>
+      </c>
+      <c r="G59" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" s="20" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="20" customHeight="1">
+      <c r="A60" s="20" t="s">
+        <v>687</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>600</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G60" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="20" customHeight="1">
+      <c r="A61" s="20" t="s">
+        <v>688</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G61" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="20" customHeight="1">
+      <c r="A62" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>609</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>601</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F62" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G62" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="20" customHeight="1">
+      <c r="A63" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F63" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G63" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="20" customHeight="1">
+      <c r="A64" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>624</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>596</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>593</v>
+      </c>
+      <c r="F64" s="20" t="s">
+        <v>582</v>
+      </c>
+      <c r="G64" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H64" s="20" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H36"/>
+  <autoFilter ref="A2:H64"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -12415,7 +13209,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -12428,19 +13222,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="26" customHeight="1">
       <c r="A1" s="81" t="s">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="B1" s="81" t="s">
-        <v>662</v>
+        <v>693</v>
       </c>
       <c r="C1" s="81" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
       <c r="D1" s="81" t="s">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="E1" s="81" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
       <c r="F1" s="81" t="s">
         <v>231</v>
@@ -12448,206 +13242,146 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1">
       <c r="A2" s="82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="B2" s="82" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="C2" s="83" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="D2" s="84">
         <v>9</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="F2" s="85" t="s">
-        <v>669</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1">
       <c r="A3" s="82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="B3" s="82" t="s">
-        <v>612</v>
+        <v>701</v>
       </c>
       <c r="C3" s="83" t="s">
-        <v>670</v>
+        <v>702</v>
       </c>
       <c r="D3" s="84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="82" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="F3" s="85" t="s">
-        <v>672</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1">
       <c r="A4" s="82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="C4" s="83" t="s">
-        <v>673</v>
+        <v>704</v>
       </c>
       <c r="D4" s="84">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="F4" s="85" t="s">
-        <v>674</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="20" customHeight="1">
       <c r="A5" s="82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>653</v>
+        <v>705</v>
       </c>
       <c r="C5" s="83" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="D5" s="84">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" s="82" t="s">
-        <v>668</v>
+        <v>699</v>
       </c>
       <c r="F5" s="85" t="s">
-        <v>676</v>
+        <v>707</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1">
       <c r="A6" s="82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>677</v>
+        <v>580</v>
       </c>
       <c r="C6" s="83" t="s">
-        <v>678</v>
+        <v>708</v>
       </c>
       <c r="D6" s="84">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E6" s="82" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1">
       <c r="A7" s="82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="C7" s="83" t="s">
-        <v>681</v>
+        <v>709</v>
       </c>
       <c r="D7" s="84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="82" t="s">
-        <v>671</v>
+        <v>699</v>
       </c>
       <c r="F7" s="85" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="20" customHeight="1">
-      <c r="A8" s="82" t="s">
-        <v>666</v>
-      </c>
-      <c r="B8" s="82" t="s">
-        <v>682</v>
-      </c>
-      <c r="C8" s="83" t="s">
-        <v>683</v>
-      </c>
-      <c r="D8" s="84">
-        <v>1</v>
-      </c>
-      <c r="E8" s="82" t="s">
-        <v>671</v>
-      </c>
-      <c r="F8" s="85" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="20" customHeight="1">
-      <c r="A9" s="82" t="s">
-        <v>666</v>
-      </c>
-      <c r="B9" s="82" t="s">
-        <v>641</v>
-      </c>
-      <c r="C9" s="83" t="s">
-        <v>684</v>
-      </c>
-      <c r="D9" s="84">
-        <v>1</v>
-      </c>
-      <c r="E9" s="82" t="s">
-        <v>671</v>
-      </c>
-      <c r="F9" s="85" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="20" customHeight="1">
-      <c r="A10" s="82" t="s">
-        <v>666</v>
-      </c>
-      <c r="B10" s="82" t="s">
-        <v>685</v>
-      </c>
-      <c r="C10" s="83" t="s">
-        <v>686</v>
-      </c>
-      <c r="D10" s="84">
-        <v>1</v>
-      </c>
-      <c r="E10" s="82" t="s">
-        <v>668</v>
-      </c>
-      <c r="F10" s="85" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="28" customHeight="1">
-      <c r="A11" s="86" t="s">
-        <v>688</v>
-      </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="87" t="s">
-        <v>689</v>
-      </c>
-      <c r="D11" s="86">
-        <v>27</v>
-      </c>
-      <c r="E11" s="86" t="s">
-        <v>690</v>
-      </c>
-      <c r="F11" s="87" t="s">
-        <v>691</v>
+        <v>703</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28" customHeight="1">
+      <c r="A8" s="86" t="s">
+        <v>710</v>
+      </c>
+      <c r="B8" s="86"/>
+      <c r="C8" s="87" t="s">
+        <v>711</v>
+      </c>
+      <c r="D8" s="86">
+        <v>40</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>712</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>713</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F7"/>
   <mergeCells count="1">
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A8:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12665,7 +13399,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="79" t="s">
-        <v>692</v>
+        <v>714</v>
       </c>
       <c r="B1" s="79"/>
       <c r="C1" s="79"/>
@@ -12677,25 +13411,25 @@
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1">
       <c r="A2" s="79" t="s">
-        <v>693</v>
+        <v>715</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="C2" s="79" t="s">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="D2" s="79" t="s">
-        <v>696</v>
+        <v>718</v>
       </c>
       <c r="E2" s="79" t="s">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="F2" s="79" t="s">
-        <v>698</v>
+        <v>720</v>
       </c>
       <c r="G2" s="79" t="s">
-        <v>699</v>
+        <v>721</v>
       </c>
       <c r="H2" s="79" t="s">
         <v>9</v>
@@ -12703,288 +13437,288 @@
     </row>
     <row r="3" spans="1:8" ht="182" customHeight="1">
       <c r="A3" s="88" t="s">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="C3" s="89" t="s">
-        <v>702</v>
+        <v>724</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>703</v>
+        <v>725</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>704</v>
+        <v>726</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>705</v>
+        <v>727</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>707</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1">
       <c r="A4" s="88" t="s">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>709</v>
+        <v>731</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>710</v>
+        <v>732</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>712</v>
+        <v>734</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>713</v>
+        <v>735</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>714</v>
+        <v>736</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1">
       <c r="A5" s="88" t="s">
-        <v>715</v>
+        <v>737</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>716</v>
+        <v>738</v>
       </c>
       <c r="C5" s="89" t="s">
-        <v>710</v>
+        <v>732</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>717</v>
+        <v>739</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>713</v>
+        <v>735</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>718</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="84" customHeight="1">
       <c r="A6" s="88" t="s">
-        <v>713</v>
+        <v>735</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>719</v>
+        <v>741</v>
       </c>
       <c r="C6" s="89" t="s">
-        <v>720</v>
+        <v>742</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>721</v>
+        <v>743</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>722</v>
+        <v>744</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>723</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42" customHeight="1">
       <c r="A7" s="88" t="s">
-        <v>724</v>
+        <v>746</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>725</v>
+        <v>747</v>
       </c>
       <c r="C7" s="89" t="s">
-        <v>726</v>
+        <v>748</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>727</v>
+        <v>749</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>728</v>
+        <v>750</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>729</v>
+        <v>751</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>730</v>
+        <v>752</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>731</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" customHeight="1">
       <c r="A8" s="88" t="s">
-        <v>732</v>
+        <v>754</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>733</v>
+        <v>755</v>
       </c>
       <c r="C8" s="89" t="s">
-        <v>734</v>
+        <v>756</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>735</v>
+        <v>757</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>736</v>
+        <v>758</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>737</v>
+        <v>759</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>738</v>
+        <v>760</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" customHeight="1">
       <c r="A9" s="88" t="s">
-        <v>739</v>
+        <v>761</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>740</v>
+        <v>762</v>
       </c>
       <c r="C9" s="89" t="s">
-        <v>741</v>
+        <v>763</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>742</v>
+        <v>764</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>743</v>
+        <v>765</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>744</v>
+        <v>766</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="90" t="s">
-        <v>746</v>
+        <v>768</v>
       </c>
       <c r="B10" s="91" t="s">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="D10" s="91" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="91" t="s">
-        <v>749</v>
+        <v>771</v>
       </c>
       <c r="F10" s="91" t="s">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="G10" s="91" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="91" t="s">
-        <v>751</v>
+        <v>773</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20" customHeight="1">
       <c r="A11" s="90" t="s">
-        <v>752</v>
+        <v>774</v>
       </c>
       <c r="B11" s="91" t="s">
-        <v>753</v>
+        <v>775</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>748</v>
+        <v>770</v>
       </c>
       <c r="D11" s="91" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="91" t="s">
-        <v>754</v>
+        <v>776</v>
       </c>
       <c r="F11" s="91" t="s">
-        <v>755</v>
+        <v>777</v>
       </c>
       <c r="G11" s="91" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="91" t="s">
-        <v>756</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20" customHeight="1">
       <c r="A12" s="90" t="s">
-        <v>757</v>
+        <v>779</v>
       </c>
       <c r="B12" s="91" t="s">
-        <v>758</v>
+        <v>780</v>
       </c>
       <c r="C12" s="89" t="s">
-        <v>759</v>
+        <v>781</v>
       </c>
       <c r="D12" s="91" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="91" t="s">
-        <v>760</v>
+        <v>782</v>
       </c>
       <c r="F12" s="91" t="s">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="G12" s="91" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="91" t="s">
-        <v>762</v>
+        <v>784</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20" customHeight="1">
       <c r="A13" s="90" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="B13" s="91" t="s">
-        <v>764</v>
+        <v>786</v>
       </c>
       <c r="C13" s="89" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="D13" s="91" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="91" t="s">
-        <v>766</v>
+        <v>788</v>
       </c>
       <c r="F13" s="91" t="s">
-        <v>767</v>
+        <v>789</v>
       </c>
       <c r="G13" s="91" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="91" t="s">
-        <v>768</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
@@ -13011,171 +13745,171 @@
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1">
       <c r="A1" s="92" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="B1" s="92"/>
       <c r="C1" s="92"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1">
       <c r="A2" s="92" t="s">
-        <v>770</v>
+        <v>792</v>
       </c>
       <c r="B2" s="92" t="s">
-        <v>771</v>
+        <v>793</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>772</v>
+        <v>794</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20" customHeight="1">
       <c r="A3" s="93" t="s">
-        <v>773</v>
+        <v>795</v>
       </c>
       <c r="B3" s="94" t="s">
-        <v>774</v>
+        <v>796</v>
       </c>
       <c r="C3" s="95" t="s">
-        <v>775</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1">
       <c r="A4" s="96" t="s">
-        <v>776</v>
+        <v>798</v>
       </c>
       <c r="B4" s="95" t="s">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="C4" s="95" t="s">
-        <v>778</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20" customHeight="1">
       <c r="A5" s="96" t="s">
-        <v>779</v>
+        <v>801</v>
       </c>
       <c r="B5" s="95" t="s">
-        <v>780</v>
+        <v>802</v>
       </c>
       <c r="C5" s="95" t="s">
-        <v>781</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20" customHeight="1">
       <c r="A6" s="96" t="s">
-        <v>782</v>
+        <v>804</v>
       </c>
       <c r="B6" s="95" t="s">
-        <v>783</v>
+        <v>805</v>
       </c>
       <c r="C6" s="95" t="s">
-        <v>784</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1">
       <c r="A7" s="96" t="s">
-        <v>785</v>
+        <v>807</v>
       </c>
       <c r="B7" s="95" t="s">
-        <v>786</v>
+        <v>808</v>
       </c>
       <c r="C7" s="95" t="s">
-        <v>787</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20" customHeight="1">
       <c r="A8" s="96" t="s">
-        <v>788</v>
+        <v>810</v>
       </c>
       <c r="B8" s="95" t="s">
-        <v>789</v>
+        <v>811</v>
       </c>
       <c r="C8" s="95" t="s">
-        <v>790</v>
+        <v>812</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20" customHeight="1">
       <c r="A9" s="96" t="s">
-        <v>791</v>
+        <v>813</v>
       </c>
       <c r="B9" s="95" t="s">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="C9" s="95" t="s">
-        <v>793</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20" customHeight="1">
       <c r="A10" s="96" t="s">
-        <v>794</v>
+        <v>816</v>
       </c>
       <c r="B10" s="95" t="s">
-        <v>795</v>
+        <v>817</v>
       </c>
       <c r="C10" s="95" t="s">
-        <v>796</v>
+        <v>818</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20" customHeight="1">
       <c r="A11" s="96" t="s">
-        <v>797</v>
+        <v>819</v>
       </c>
       <c r="B11" s="95" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="C11" s="95" t="s">
-        <v>799</v>
+        <v>821</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1">
       <c r="A12" s="97" t="s">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="B12" s="98" t="s">
-        <v>801</v>
+        <v>823</v>
       </c>
       <c r="C12" s="95" t="s">
-        <v>802</v>
+        <v>824</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="20" customHeight="1">
       <c r="A13" s="99" t="s">
-        <v>800</v>
+        <v>822</v>
       </c>
       <c r="B13" s="100" t="s">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>804</v>
+        <v>826</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20" customHeight="1">
       <c r="A14" s="101" t="s">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="B14" s="102" t="s">
-        <v>806</v>
+        <v>828</v>
       </c>
       <c r="C14" s="95" t="s">
-        <v>807</v>
+        <v>829</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20" customHeight="1">
       <c r="A15" s="96" t="s">
-        <v>808</v>
+        <v>830</v>
       </c>
       <c r="B15" s="95" t="s">
-        <v>809</v>
+        <v>831</v>
       </c>
       <c r="C15" s="95" t="s">
-        <v>810</v>
+        <v>832</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20" customHeight="1">
       <c r="A16" s="96" t="s">
-        <v>811</v>
+        <v>833</v>
       </c>
       <c r="B16" s="95" t="s">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="C16" s="103" t="s">
         <v>22</v>
@@ -13183,7 +13917,7 @@
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1">
       <c r="A17" s="103" t="s">
-        <v>813</v>
+        <v>835</v>
       </c>
       <c r="B17" s="103"/>
       <c r="C17" s="103"/>

--- a/ROCm_CICD_Comprehensive.xlsx
+++ b/ROCm_CICD_Comprehensive.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3042" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3039" uniqueCount="833">
   <si>
     <t>Category</t>
   </si>
@@ -97,8 +97,8 @@
     <t>gfx94X-dcgpu (Build + Test)</t>
   </si>
   <si>
-    <t>linux-gfx942-1gpu-ossci-rocm
-(alternate pool: linux-gfx942-1gpu-ccs-ossci-rocm, linux-gfx942-1gpu-core42-ossci-rocm)</t>
+    <t>linux-gfx942-1gpu-core42-ossci-rocm
+(alternate pool: linux-gfx942-1gpu-ccs-ossci-rocm, linux-gfx942-1gpu-ossci-rocm)</t>
   </si>
   <si>
     <t>—</t>
@@ -113,7 +113,7 @@
     <t>linux-gfx110X-gpu-rocm (gfx110X-all)
 linux-gfx1151-gpu-rocm (gfx1151)
 linux-gfx120X-gpu-rocm (gfx120X-all)
-linux-gfx942-1gpu-ossci-rocm (gfx94X-dcgpu)
+linux-gfx942-1gpu-core42-ossci-rocm (gfx94X-dcgpu)
 linux-gfx950-1gpu-ccs-ossci-rocm (gfx950-dcgpu)</t>
   </si>
   <si>
@@ -121,7 +121,7 @@
   </si>
   <si>
     <t>gfx103X-all, gfx110X-all, gfx1150, gfx1151, gfx1153, gfx120X-all, gfx90a, gfx94X-dcgpu, gfx950-dcgpu
-(Build-only: gfx101X-dgpu, gfx1152, gfx900, gfx906, gfx908)</t>
+(Build-only: gfx101X-dgpu, gfx1152, gfx125X-dcgpu, gfx900, gfx906, gfx908)</t>
   </si>
   <si>
     <t>linux-gfx1030-gpu-rocm (gfx103X-all)
@@ -131,7 +131,7 @@
 linux-gfx1153-gpu-rocm (gfx1153)
 linux-gfx120X-gpu-rocm (gfx120X-all)
 linux-gfx90a-gpu-rocm (gfx90a)
-linux-gfx942-1gpu-ossci-rocm (gfx94X-dcgpu)
+linux-gfx942-1gpu-core42-ossci-rocm (gfx94X-dcgpu)
 linux-gfx950-1gpu-ccs-ossci-rocm (gfx950-dcgpu)</t>
   </si>
   <si>
@@ -1007,12 +1007,11 @@
     <t>Windows Server 2022</t>
   </si>
   <si>
-    <t>ci_nightly.yml + ci_nightly_pytorch_full_test.yml
-(schedule + workflow_dispatch)</t>
+    <t>multi_arch_ci_asan.yml (schedule) + test_pytorch_wheels_full.yml (workflow_dispatch)</t>
   </si>
   <si>
     <t>02:00 UTC daily (ROCm) — cron: 0 02 * * *
-12:00 UTC daily (PyTorch full) — cron: 0 12 * * *</t>
+PyTorch full suite: on-demand (workflow_dispatch)</t>
   </si>
   <si>
     <t>comprehensive = full + integration (ROCm)
@@ -1037,16 +1036,16 @@
     <t>ASAN / TSAN</t>
   </si>
   <si>
-    <t>ASAN: ci_asan.yml — workflow_dispatch ONLY (no schedule; legacy workflow scheduled for removal)
-TSAN: ci_tsan.yml — schedule + workflow_dispatch</t>
-  </si>
-  <si>
-    <t>ASAN: on-demand only
-TSAN: 02:00 UTC daily — cron: 0 02 * * *</t>
+    <t>ASAN + TSAN: multi_arch_ci_asan.yml — push to main + schedule + workflow_dispatch
+(consolidated the retired ci_asan.yml / ci_tsan.yml)</t>
+  </si>
+  <si>
+    <t>02:00 UTC daily — cron: 0 02 * * *
++ on push to main &amp; on-demand</t>
   </si>
   <si>
     <t>quick = smoke/sanity only
-(asan/tsan variants of ci_linux.yml — sanitizer-instrumented build of post-commit suite)</t>
+(asan/host-asan/tsan build variants from amdgpu_family_matrix.py, via multi_arch_ci_linux.yml — sanitizer-instrumented build of post-commit suite)</t>
   </si>
   <si>
     <t>Build + Test:
@@ -1861,7 +1860,7 @@
     <t>CI pipeline (post-merge push to release/2.9)</t>
   </si>
   <si>
-    <t>CI pipeline (post-merge push to release/2.10) + 02:00 UTC daily (ci_nightly.yml)</t>
+    <t>CI pipeline (post-merge push to release/2.10) + 02:00 UTC daily (multi_arch_ci_asan.yml)</t>
   </si>
   <si>
     <t>Default CI pin branch</t>
@@ -1870,7 +1869,7 @@
     <t>CI pipeline (post-merge push to release/2.11)</t>
   </si>
   <si>
-    <t>02:00 UTC daily (ci_nightly.yml) + on push to pytorch/pytorch main</t>
+    <t>02:00 UTC daily (multi_arch_ci_asan.yml) + on push to pytorch/pytorch main</t>
   </si>
   <si>
     <t>jaxlib, jax_rocm7_plugin, jax_rocm7_pjrt</t>
@@ -2624,55 +2623,46 @@
     <t>https://github.com/ROCm/TheRock/blob/main/.gitmodules</t>
   </si>
   <si>
-    <t>ci_nightly.yml</t>
-  </si>
-  <si>
-    <t>Nightly schedule time, GPU family test matrix for the nightly tier</t>
-  </si>
-  <si>
-    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci_nightly.yml</t>
-  </si>
-  <si>
-    <t>ci.yml</t>
-  </si>
-  <si>
-    <t>Pre-commit tier — PR trigger, quick builds across core GPU families</t>
-  </si>
-  <si>
-    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci.yml</t>
-  </si>
-  <si>
-    <t>ci_asan.yml</t>
-  </si>
-  <si>
-    <t>ASAN sanitizer builds (gfx94X test pool)</t>
-  </si>
-  <si>
-    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci_asan.yml</t>
-  </si>
-  <si>
-    <t>ci_tsan.yml</t>
-  </si>
-  <si>
-    <t>TSAN sanitizer builds</t>
-  </si>
-  <si>
-    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/ci_tsan.yml</t>
+    <t>multi_arch_ci_asan.yml</t>
+  </si>
+  <si>
+    <t>Nightly schedule (cron '0 02 * * *') + ASAN sanitizer test matrix</t>
+  </si>
+  <si>
+    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/multi_arch_ci_asan.yml</t>
+  </si>
+  <si>
+    <t>pre-commit.yml</t>
+  </si>
+  <si>
+    <t>Pre-commit tier — lint/format checks on PR + push to main</t>
+  </si>
+  <si>
+    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/pre-commit.yml</t>
   </si>
   <si>
     <t>multi_arch_ci.yml</t>
   </si>
   <si>
-    <t>Multi-arch CI matrix (Linux + Windows GPU families)</t>
+    <t>Main CI — push to main / release branches + workflow_dispatch (Linux + Windows GPU families)</t>
   </si>
   <si>
     <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/multi_arch_ci.yml</t>
   </si>
   <si>
+    <t>multi_arch_ci_linux.yml / _windows.yml</t>
+  </si>
+  <si>
+    <t>Reusable per-platform CI sub-workflows (workflow_call)</t>
+  </si>
+  <si>
+    <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/multi_arch_ci_linux.yml</t>
+  </si>
+  <si>
     <t>multi_arch_release.yml</t>
   </si>
   <si>
-    <t>Release pipeline (workflow_dispatch)</t>
+    <t>Release pipeline (workflow_call: dev / nightly / prerelease)</t>
   </si>
   <si>
     <t>https://github.com/ROCm/TheRock/blob/main/.github/workflows/multi_arch_release.yml</t>
@@ -3854,12 +3844,12 @@
     <col min="9" max="9" width="39.7109375" customWidth="1"/>
     <col min="10" max="10" width="26.7109375" customWidth="1"/>
     <col min="11" max="11" width="60.7109375" customWidth="1"/>
-    <col min="12" max="12" width="49.7109375" customWidth="1"/>
+    <col min="12" max="12" width="52.7109375" customWidth="1"/>
     <col min="13" max="13" width="48.7109375" customWidth="1"/>
     <col min="14" max="14" width="39.7109375" customWidth="1"/>
     <col min="15" max="15" width="26.7109375" customWidth="1"/>
     <col min="16" max="16" width="60.7109375" customWidth="1"/>
-    <col min="17" max="17" width="50.7109375" customWidth="1"/>
+    <col min="17" max="17" width="52.7109375" customWidth="1"/>
     <col min="18" max="18" width="48.7109375" customWidth="1"/>
     <col min="19" max="19" width="40.7109375" customWidth="1"/>
     <col min="20" max="20" width="26.7109375" customWidth="1"/>
@@ -13735,7 +13725,7 @@
   <sheetPr>
     <tabColor rgb="FF78909C"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -13850,10 +13840,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="20" customHeight="1">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="97" t="s">
         <v>819</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="98" t="s">
         <v>820</v>
       </c>
       <c r="C11" s="95" t="s">
@@ -13861,21 +13851,21 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="20" customHeight="1">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="99" t="s">
+        <v>819</v>
+      </c>
+      <c r="B12" s="100" t="s">
         <v>822</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="C12" s="95" t="s">
         <v>823</v>
       </c>
-      <c r="C12" s="95" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="20" customHeight="1">
+      <c r="A13" s="101" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="20" customHeight="1">
-      <c r="A13" s="99" t="s">
-        <v>822</v>
-      </c>
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="102" t="s">
         <v>825</v>
       </c>
       <c r="C13" s="95" t="s">
@@ -13883,10 +13873,10 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="20" customHeight="1">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="96" t="s">
         <v>827</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="95" t="s">
         <v>828</v>
       </c>
       <c r="C14" s="95" t="s">
@@ -13900,32 +13890,21 @@
       <c r="B15" s="95" t="s">
         <v>831</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" customHeight="1">
+      <c r="A16" s="103" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="20" customHeight="1">
-      <c r="A16" s="96" t="s">
-        <v>833</v>
-      </c>
-      <c r="B16" s="95" t="s">
-        <v>834</v>
-      </c>
-      <c r="C16" s="103" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" customHeight="1">
-      <c r="A17" s="103" t="s">
-        <v>835</v>
-      </c>
-      <c r="B17" s="103"/>
-      <c r="C17" s="103"/>
+      <c r="B16" s="103"/>
+      <c r="C16" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1"/>
@@ -13940,7 +13919,6 @@
     <hyperlink ref="C12" r:id="rId10"/>
     <hyperlink ref="C13" r:id="rId11"/>
     <hyperlink ref="C14" r:id="rId12"/>
-    <hyperlink ref="C15" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
